--- a/AsymReca_ThkCalc_new.xlsx
+++ b/AsymReca_ThkCalc_new.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2024-ILLUSTRIOUS\My Drive (61050734@kmitl.ac.th)\AsymReca_SbSe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B44330-8831-49A8-BF7A-4062FB572187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6001A2C2-D615-46B1-BBDA-700EE9B9082D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="-120" windowWidth="28200" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28200" yWindow="5265" windowWidth="28320" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="532_back" sheetId="15" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="166">
   <si>
     <t>Wavelength (nm)</t>
   </si>
@@ -2109,6 +2109,30 @@
   </si>
   <si>
     <t>λ = 532</t>
+  </si>
+  <si>
+    <t>FP</t>
+  </si>
+  <si>
+    <t>U = H/2 L H/2</t>
+  </si>
+  <si>
+    <t>N1 SbSe M1</t>
+  </si>
+  <si>
+    <t>H =TiO2</t>
+  </si>
+  <si>
+    <t>N2 SbSe M1</t>
+  </si>
+  <si>
+    <t>N2 SbSe/TiO M2</t>
+  </si>
+  <si>
+    <t>N1 SbSe/TiO M1</t>
+  </si>
+  <si>
+    <t>N3 SbSe/TiO M3</t>
   </si>
 </sst>
 </file>
@@ -2483,7 +2507,7 @@
     <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="192">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2894,6 +2918,21 @@
     <xf numFmtId="164" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2909,42 +2948,36 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2966,15 +2999,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -2984,20 +3017,35 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3017,44 +3065,8 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3542,59 +3554,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="145" t="s">
+      <c r="A1" s="148" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="153" t="s">
+      <c r="B1" s="150" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="147" t="s">
+      <c r="C1" s="152" t="s">
         <v>121</v>
       </c>
       <c r="D1" s="44" t="s">
         <v>98</v>
       </c>
-      <c r="E1" s="141" t="s">
+      <c r="E1" s="146" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="151" t="s">
+      <c r="F1" s="155" t="s">
         <v>115</v>
       </c>
-      <c r="G1" s="143" t="s">
+      <c r="G1" s="141" t="s">
         <v>116</v>
       </c>
-      <c r="H1" s="138" t="s">
+      <c r="H1" s="143" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="140" t="s">
+      <c r="I1" s="145" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="141"/>
-      <c r="K1" s="142"/>
-      <c r="L1" s="140" t="s">
+      <c r="J1" s="146"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="145" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="141"/>
-      <c r="N1" s="142"/>
-      <c r="O1" s="140" t="s">
+      <c r="M1" s="146"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="145" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="141"/>
-      <c r="Q1" s="142"/>
+      <c r="P1" s="146"/>
+      <c r="Q1" s="147"/>
       <c r="S1" s="128"/>
       <c r="T1" s="128"/>
       <c r="U1" s="128"/>
       <c r="V1" s="128"/>
     </row>
     <row r="2" spans="1:22" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="146"/>
-      <c r="B2" s="154"/>
-      <c r="C2" s="148"/>
+      <c r="A2" s="149"/>
+      <c r="B2" s="151"/>
+      <c r="C2" s="153"/>
       <c r="D2" s="44"/>
-      <c r="E2" s="150"/>
-      <c r="F2" s="152"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="139"/>
+      <c r="E2" s="154"/>
+      <c r="F2" s="156"/>
+      <c r="G2" s="142"/>
+      <c r="H2" s="144"/>
       <c r="I2" s="111" t="s">
         <v>36</v>
       </c>
@@ -3633,7 +3645,7 @@
         <v>532</v>
       </c>
       <c r="B3" s="35"/>
-      <c r="C3" s="185" t="s">
+      <c r="C3" s="37" t="s">
         <v>74</v>
       </c>
       <c r="D3" s="44">
@@ -3743,12 +3755,11 @@
         <f t="shared" si="2"/>
         <v>-0.18</v>
       </c>
-      <c r="R4" s="187"/>
-      <c r="S4" s="188"/>
+      <c r="S4" s="131"/>
     </row>
     <row r="5" spans="1:22" s="30" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B5" s="35"/>
-      <c r="C5" s="186" t="s">
+      <c r="C5" s="38" t="s">
         <v>123</v>
       </c>
       <c r="D5" s="44">
@@ -3761,7 +3772,7 @@
         <v>134.29</v>
       </c>
       <c r="G5" s="134">
-        <f>F5</f>
+        <f t="shared" ref="G5:G10" si="3">F5</f>
         <v>134.29</v>
       </c>
       <c r="H5" s="135">
@@ -3803,7 +3814,7 @@
     </row>
     <row r="6" spans="1:22" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="35"/>
-      <c r="C6" s="186" t="s">
+      <c r="C6" s="38" t="s">
         <v>122</v>
       </c>
       <c r="D6" s="44">
@@ -3816,7 +3827,7 @@
         <v>67.150000000000006</v>
       </c>
       <c r="G6" s="134">
-        <f>F6</f>
+        <f t="shared" si="3"/>
         <v>67.150000000000006</v>
       </c>
       <c r="H6" s="135">
@@ -3858,7 +3869,7 @@
     </row>
     <row r="7" spans="1:22" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="35"/>
-      <c r="C7" s="186" t="s">
+      <c r="C7" s="38" t="s">
         <v>125</v>
       </c>
       <c r="D7" s="44">
@@ -3871,7 +3882,7 @@
         <v>33.57</v>
       </c>
       <c r="G7" s="134">
-        <f>F7</f>
+        <f t="shared" si="3"/>
         <v>33.57</v>
       </c>
       <c r="H7" s="135">
@@ -3910,7 +3921,7 @@
       <c r="S7" s="131"/>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C8" s="186" t="s">
+      <c r="C8" s="38" t="s">
         <v>105</v>
       </c>
       <c r="D8" s="44">
@@ -3923,7 +3934,7 @@
         <v>33.57</v>
       </c>
       <c r="G8" s="134">
-        <f>F8</f>
+        <f t="shared" si="3"/>
         <v>33.57</v>
       </c>
       <c r="H8" s="136">
@@ -3977,7 +3988,7 @@
         <v>22.6</v>
       </c>
       <c r="G9" s="134">
-        <f>F9</f>
+        <f t="shared" si="3"/>
         <v>22.6</v>
       </c>
       <c r="H9" s="136">
@@ -4016,7 +4027,7 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B10" s="71"/>
-      <c r="C10" s="186" t="s">
+      <c r="C10" s="38" t="s">
         <v>105</v>
       </c>
       <c r="D10" s="44">
@@ -4029,7 +4040,7 @@
         <v>43.7</v>
       </c>
       <c r="G10" s="134">
-        <f>F10</f>
+        <f t="shared" si="3"/>
         <v>43.7</v>
       </c>
       <c r="H10" s="136">
@@ -4068,7 +4079,6 @@
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B11" s="71"/>
-      <c r="C11" s="186"/>
       <c r="F11" s="84"/>
       <c r="G11" s="134"/>
       <c r="K11" s="90"/>
@@ -4079,7 +4089,7 @@
       <c r="B12" s="35" t="s">
         <v>100</v>
       </c>
-      <c r="C12" s="186" t="s">
+      <c r="C12" s="38" t="s">
         <v>103</v>
       </c>
       <c r="D12" s="44">
@@ -4131,7 +4141,7 @@
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="30"/>
-      <c r="C13" s="186" t="s">
+      <c r="C13" s="38" t="s">
         <v>102</v>
       </c>
       <c r="D13" s="44">
@@ -4182,7 +4192,7 @@
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C14" s="186" t="s">
+      <c r="C14" s="38" t="s">
         <v>101</v>
       </c>
       <c r="D14" s="44">
@@ -4234,7 +4244,7 @@
     </row>
     <row r="15" spans="1:22" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="32"/>
-      <c r="C15" s="186" t="s">
+      <c r="C15" s="38" t="s">
         <v>99</v>
       </c>
       <c r="D15" s="44">
@@ -4290,7 +4300,7 @@
     </row>
     <row r="16" spans="1:22" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="32"/>
-      <c r="C16" s="186"/>
+      <c r="C16" s="38"/>
       <c r="D16" s="44"/>
       <c r="E16" s="34"/>
       <c r="F16" s="34"/>
@@ -4317,7 +4327,7 @@
       <c r="B17" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="C17" s="186" t="s">
+      <c r="C17" s="38" t="s">
         <v>141</v>
       </c>
       <c r="D17" s="44">
@@ -4343,7 +4353,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
       <c r="K17" s="90">
-        <f t="shared" ref="K17:K20" si="3">I17-J17</f>
+        <f t="shared" ref="K17:K20" si="4">I17-J17</f>
         <v>0.184</v>
       </c>
       <c r="L17" s="92">
@@ -4353,7 +4363,7 @@
         <v>0.874</v>
       </c>
       <c r="N17" s="90">
-        <f t="shared" ref="N17:N20" si="4">L17-M17</f>
+        <f t="shared" ref="N17:N20" si="5">L17-M17</f>
         <v>-0.11899999999999999</v>
       </c>
       <c r="O17" s="92">
@@ -4363,7 +4373,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
       <c r="Q17" s="90">
-        <f t="shared" ref="Q17:Q20" si="5">O17-P17</f>
+        <f t="shared" ref="Q17:Q20" si="6">O17-P17</f>
         <v>-6.5000000000000002E-2</v>
       </c>
       <c r="S17" s="32"/>
@@ -4375,7 +4385,7 @@
       <c r="A18" s="32" t="s">
         <v>140</v>
       </c>
-      <c r="C18" s="186" t="s">
+      <c r="C18" s="38" t="s">
         <v>142</v>
       </c>
       <c r="D18" s="44">
@@ -4401,7 +4411,7 @@
         <v>0.02</v>
       </c>
       <c r="K18" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8.1000000000000003E-2</v>
       </c>
       <c r="L18" s="92">
@@ -4411,7 +4421,7 @@
         <v>0.86399999999999999</v>
       </c>
       <c r="N18" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.5000000000000031E-2</v>
       </c>
       <c r="O18" s="92">
@@ -4421,7 +4431,7 @@
         <v>0.115</v>
       </c>
       <c r="Q18" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.115</v>
       </c>
       <c r="S18" s="32"/>
@@ -4433,7 +4443,7 @@
       <c r="A19" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="C19" s="186" t="s">
+      <c r="C19" s="38" t="s">
         <v>143</v>
       </c>
       <c r="D19" s="44">
@@ -4458,7 +4468,7 @@
         <v>0.153</v>
       </c>
       <c r="K19" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.18200000000000002</v>
       </c>
       <c r="L19" s="92">
@@ -4468,7 +4478,7 @@
         <v>0.73499999999999999</v>
       </c>
       <c r="N19" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-7.3999999999999955E-2</v>
       </c>
       <c r="O19" s="92">
@@ -4478,7 +4488,7 @@
         <v>0.112</v>
       </c>
       <c r="Q19" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.108</v>
       </c>
       <c r="S19" s="32"/>
@@ -4490,7 +4500,7 @@
       <c r="A20" s="32" t="s">
         <v>139</v>
       </c>
-      <c r="C20" s="186" t="s">
+      <c r="C20" s="38" t="s">
         <v>144</v>
       </c>
       <c r="D20" s="44">
@@ -4516,7 +4526,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="K20" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.8000000000000004E-2</v>
       </c>
       <c r="L20" s="92">
@@ -4526,7 +4536,7 @@
         <v>0.85899999999999999</v>
       </c>
       <c r="N20" s="42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.10599999999999998</v>
       </c>
       <c r="O20" s="92">
@@ -4536,7 +4546,7 @@
         <v>0.13500000000000001</v>
       </c>
       <c r="Q20" s="42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.13500000000000001</v>
       </c>
       <c r="S20" s="32"/>
@@ -4546,7 +4556,7 @@
     </row>
     <row r="21" spans="1:22" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="32"/>
-      <c r="C21" s="186" t="s">
+      <c r="C21" s="38" t="s">
         <v>145</v>
       </c>
       <c r="D21" s="44">
@@ -4601,7 +4611,7 @@
     </row>
     <row r="22" spans="1:22" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="32"/>
-      <c r="C22" s="186" t="s">
+      <c r="C22" s="38" t="s">
         <v>146</v>
       </c>
       <c r="D22" s="44">
@@ -4714,7 +4724,7 @@
     </row>
     <row r="24" spans="1:22" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="32"/>
-      <c r="C24" s="186" t="s">
+      <c r="C24" s="38" t="s">
         <v>154</v>
       </c>
       <c r="D24" s="32">
@@ -4740,7 +4750,7 @@
         <v>0.15</v>
       </c>
       <c r="K24" s="90">
-        <f t="shared" ref="K24:K25" si="6">I24-J24</f>
+        <f t="shared" ref="K24:K25" si="7">I24-J24</f>
         <v>0.18400000000000002</v>
       </c>
       <c r="L24" s="35">
@@ -4750,7 +4760,7 @@
         <v>0.751</v>
       </c>
       <c r="N24" s="90">
-        <f t="shared" ref="N24:N25" si="7">L24-M24</f>
+        <f t="shared" ref="N24:N25" si="8">L24-M24</f>
         <v>-8.8999999999999968E-2</v>
       </c>
       <c r="O24" s="35">
@@ -4760,7 +4770,7 @@
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="Q24" s="90">
-        <f t="shared" ref="Q24:Q25" si="8">O24-P24</f>
+        <f t="shared" ref="Q24:Q25" si="9">O24-P24</f>
         <v>-9.5000000000000001E-2</v>
       </c>
       <c r="S24" s="32"/>
@@ -4769,7 +4779,7 @@
       <c r="V24" s="32"/>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C25" s="186" t="s">
+      <c r="C25" s="38" t="s">
         <v>155</v>
       </c>
       <c r="D25" s="44">
@@ -4795,7 +4805,7 @@
         <v>0.17599999999999999</v>
       </c>
       <c r="K25" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.22200000000000003</v>
       </c>
       <c r="L25" s="92">
@@ -4805,7 +4815,7 @@
         <v>0.57299999999999995</v>
       </c>
       <c r="N25" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-3.7999999999999923E-2</v>
       </c>
       <c r="O25" s="92">
@@ -4815,13 +4825,13 @@
         <v>0.252</v>
       </c>
       <c r="Q25" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-0.185</v>
       </c>
     </row>
     <row r="26" spans="1:22" s="35" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="C26" s="186"/>
-      <c r="J26" s="190"/>
+      <c r="C26" s="38"/>
+      <c r="J26" s="139"/>
       <c r="S26" s="32"/>
       <c r="T26" s="32"/>
       <c r="U26" s="32"/>
@@ -4831,7 +4841,7 @@
       <c r="B27" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="C27" s="186" t="s">
+      <c r="C27" s="38" t="s">
         <v>147</v>
       </c>
       <c r="D27" s="44">
@@ -4856,7 +4866,7 @@
         <v>0.14399999999999999</v>
       </c>
       <c r="K27" s="90">
-        <f>I27-J27</f>
+        <f t="shared" ref="K27:K32" si="10">I27-J27</f>
         <v>0.23800000000000002</v>
       </c>
       <c r="L27" s="92">
@@ -4866,7 +4876,7 @@
         <v>0.78800000000000003</v>
       </c>
       <c r="N27" s="90">
-        <f>L27-M27</f>
+        <f t="shared" ref="N27:N32" si="11">L27-M27</f>
         <v>-0.17500000000000004</v>
       </c>
       <c r="O27" s="92">
@@ -4876,7 +4886,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
       <c r="Q27" s="90">
-        <f>O27-P27</f>
+        <f t="shared" ref="Q27:Q32" si="12">O27-P27</f>
         <v>-6.3E-2</v>
       </c>
       <c r="S27" s="32"/>
@@ -4885,7 +4895,7 @@
       <c r="V27" s="32"/>
     </row>
     <row r="28" spans="1:22" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="186" t="s">
+      <c r="C28" s="38" t="s">
         <v>148</v>
       </c>
       <c r="D28" s="44">
@@ -4910,7 +4920,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="K28" s="97">
-        <f>I28-J28</f>
+        <f t="shared" si="10"/>
         <v>8.900000000000001E-2</v>
       </c>
       <c r="L28" s="92">
@@ -4920,7 +4930,7 @@
         <v>0.84799999999999998</v>
       </c>
       <c r="N28" s="97">
-        <f>L28-M28</f>
+        <f t="shared" si="11"/>
         <v>3.400000000000003E-2</v>
       </c>
       <c r="O28" s="92">
@@ -4930,7 +4940,7 @@
         <v>0.124</v>
       </c>
       <c r="Q28" s="97">
-        <f>O28-P28</f>
+        <f t="shared" si="12"/>
         <v>-0.123</v>
       </c>
       <c r="S28" s="32"/>
@@ -4964,7 +4974,7 @@
         <v>0.216</v>
       </c>
       <c r="K29" s="97">
-        <f>I29-J29</f>
+        <f t="shared" si="10"/>
         <v>0.22600000000000001</v>
       </c>
       <c r="L29" s="92">
@@ -4974,7 +4984,7 @@
         <v>0.69499999999999995</v>
       </c>
       <c r="N29" s="97">
-        <f>L29-M29</f>
+        <f t="shared" si="11"/>
         <v>-0.14499999999999991</v>
       </c>
       <c r="O29" s="92">
@@ -4984,7 +4994,7 @@
         <v>8.8999999999999996E-2</v>
       </c>
       <c r="Q29" s="97">
-        <f>O29-P29</f>
+        <f t="shared" si="12"/>
         <v>-8.199999999999999E-2</v>
       </c>
       <c r="S29" s="32"/>
@@ -4993,7 +5003,7 @@
       <c r="V29" s="32"/>
     </row>
     <row r="30" spans="1:22" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C30" s="186" t="s">
+      <c r="C30" s="38" t="s">
         <v>150</v>
       </c>
       <c r="D30" s="44">
@@ -5018,7 +5028,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="K30" s="97">
-        <f>I30-J30</f>
+        <f t="shared" si="10"/>
         <v>0.113</v>
       </c>
       <c r="L30" s="92">
@@ -5028,7 +5038,7 @@
         <v>0.90600000000000003</v>
       </c>
       <c r="N30" s="97">
-        <f>L30-M30</f>
+        <f t="shared" si="11"/>
         <v>-8.9000000000000079E-2</v>
       </c>
       <c r="O30" s="92">
@@ -5038,7 +5048,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="Q30" s="97">
-        <f>O30-P30</f>
+        <f t="shared" si="12"/>
         <v>-2.4E-2</v>
       </c>
       <c r="S30" s="32"/>
@@ -5047,7 +5057,7 @@
       <c r="V30" s="32"/>
     </row>
     <row r="31" spans="1:22" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C31" s="186" t="s">
+      <c r="C31" s="38" t="s">
         <v>151</v>
       </c>
       <c r="D31" s="44">
@@ -5072,7 +5082,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="K31" s="97">
-        <f>I31-J31</f>
+        <f t="shared" si="10"/>
         <v>8.5999999999999993E-2</v>
       </c>
       <c r="L31" s="92">
@@ -5082,7 +5092,7 @@
         <v>0.85499999999999998</v>
       </c>
       <c r="N31" s="97">
-        <f>L31-M31</f>
+        <f t="shared" si="11"/>
         <v>3.3000000000000029E-2</v>
       </c>
       <c r="O31" s="92">
@@ -5092,7 +5102,7 @@
         <v>0.12</v>
       </c>
       <c r="Q31" s="97">
-        <f>O31-P31</f>
+        <f t="shared" si="12"/>
         <v>-0.11899999999999999</v>
       </c>
       <c r="S31" s="32"/>
@@ -5101,7 +5111,7 @@
       <c r="V31" s="32"/>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C32" s="186" t="s">
+      <c r="C32" s="38" t="s">
         <v>152</v>
       </c>
       <c r="D32" s="44">
@@ -5126,7 +5136,7 @@
         <v>0.21199999999999999</v>
       </c>
       <c r="K32" s="97">
-        <f>I32-J32</f>
+        <f t="shared" si="10"/>
         <v>0.23</v>
       </c>
       <c r="L32" s="92">
@@ -5136,7 +5146,7 @@
         <v>0.70699999999999996</v>
       </c>
       <c r="N32" s="97">
-        <f>L32-M32</f>
+        <f t="shared" si="11"/>
         <v>-0.15599999999999992</v>
       </c>
       <c r="O32" s="92">
@@ -5146,12 +5156,12 @@
         <v>8.2000000000000003E-2</v>
       </c>
       <c r="Q32" s="97">
-        <f>O32-P32</f>
+        <f t="shared" si="12"/>
         <v>-7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="191" t="s">
+      <c r="A36" s="140" t="s">
         <v>157</v>
       </c>
       <c r="B36" s="69" t="s">
@@ -5220,7 +5230,7 @@
       <c r="A42" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="B42" s="189">
+      <c r="B42" s="138">
         <v>3.9615</v>
       </c>
       <c r="C42" s="45">
@@ -5251,16 +5261,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
   </mergeCells>
   <conditionalFormatting sqref="K35:K1048576 K27:K32 K1:K25">
     <cfRule type="top10" dxfId="17" priority="9" percent="1" rank="25"/>
@@ -5298,66 +5308,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="166" t="s">
+      <c r="A1" s="169" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="145" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="167" t="s">
+      <c r="B1" s="148" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="170" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="147" t="s">
+      <c r="D1" s="152" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="140" t="s">
+      <c r="E1" s="145" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="141" t="s">
+      <c r="F1" s="146" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="159" t="s">
+      <c r="G1" s="162" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="159" t="s">
+      <c r="H1" s="162" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="141" t="s">
+      <c r="I1" s="146" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="155" t="s">
+      <c r="J1" s="158" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="140" t="s">
+      <c r="K1" s="145" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="141"/>
-      <c r="M1" s="142"/>
-      <c r="N1" s="140" t="s">
+      <c r="L1" s="146"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="145" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="141"/>
-      <c r="P1" s="142"/>
-      <c r="Q1" s="140" t="s">
+      <c r="O1" s="146"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="145" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="141"/>
-      <c r="S1" s="142"/>
-      <c r="T1" s="168" t="s">
+      <c r="R1" s="146"/>
+      <c r="S1" s="147"/>
+      <c r="T1" s="174" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:25" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="150"/>
-      <c r="B2" s="146"/>
-      <c r="C2" s="161"/>
-      <c r="D2" s="148"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="150"/>
-      <c r="G2" s="146"/>
-      <c r="H2" s="146"/>
-      <c r="I2" s="150"/>
-      <c r="J2" s="156"/>
+      <c r="A2" s="154"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="164"/>
+      <c r="D2" s="153"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="154"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="154"/>
+      <c r="J2" s="159"/>
       <c r="K2" s="39" t="s">
         <v>36</v>
       </c>
@@ -5385,11 +5395,11 @@
       <c r="S2" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="T2" s="169"/>
-      <c r="V2" s="150"/>
-      <c r="W2" s="150"/>
-      <c r="X2" s="150"/>
-      <c r="Y2" s="150"/>
+      <c r="T2" s="175"/>
+      <c r="V2" s="154"/>
+      <c r="W2" s="154"/>
+      <c r="X2" s="154"/>
+      <c r="Y2" s="154"/>
     </row>
     <row r="3" spans="1:25" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="30">
@@ -5401,10 +5411,10 @@
       <c r="D3" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="170">
-        <v>0</v>
-      </c>
-      <c r="F3" s="172">
+      <c r="E3" s="171">
+        <v>0</v>
+      </c>
+      <c r="F3" s="173">
         <v>0</v>
       </c>
       <c r="G3" s="58">
@@ -5456,8 +5466,8 @@
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="E4" s="171"/>
-      <c r="F4" s="164"/>
+      <c r="E4" s="172"/>
+      <c r="F4" s="165"/>
       <c r="G4" s="58">
         <v>35.6</v>
       </c>
@@ -5510,10 +5520,10 @@
       <c r="D5" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="162">
+      <c r="E5" s="166">
         <v>32.700000000000003</v>
       </c>
-      <c r="F5" s="163">
+      <c r="F5" s="167">
         <v>90.1</v>
       </c>
       <c r="G5" s="58">
@@ -5566,8 +5576,8 @@
       <c r="D6" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="162"/>
-      <c r="F6" s="163"/>
+      <c r="E6" s="166"/>
+      <c r="F6" s="167"/>
       <c r="G6" s="58">
         <v>35.6</v>
       </c>
@@ -5690,10 +5700,10 @@
       <c r="D9" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="162">
+      <c r="E9" s="166">
         <v>66.599999999999994</v>
       </c>
-      <c r="F9" s="163">
+      <c r="F9" s="167">
         <v>181.3</v>
       </c>
       <c r="G9" s="58">
@@ -5745,8 +5755,8 @@
       <c r="D10" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="162"/>
-      <c r="F10" s="163"/>
+      <c r="E10" s="166"/>
+      <c r="F10" s="167"/>
       <c r="G10" s="58">
         <v>75.8</v>
       </c>
@@ -5796,8 +5806,8 @@
       <c r="D11" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="162"/>
-      <c r="F11" s="163"/>
+      <c r="E11" s="166"/>
+      <c r="F11" s="167"/>
       <c r="G11" s="58">
         <v>89.5</v>
       </c>
@@ -5845,8 +5855,8 @@
       <c r="D12" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="162"/>
-      <c r="F12" s="163"/>
+      <c r="E12" s="166"/>
+      <c r="F12" s="167"/>
       <c r="G12" s="58">
         <v>46.1</v>
       </c>
@@ -5896,8 +5906,8 @@
       <c r="D13" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="162"/>
-      <c r="F13" s="163"/>
+      <c r="E13" s="166"/>
+      <c r="F13" s="167"/>
       <c r="G13" s="58">
         <v>73.400000000000006</v>
       </c>
@@ -5946,8 +5956,8 @@
       <c r="D14" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="162"/>
-      <c r="F14" s="163"/>
+      <c r="E14" s="166"/>
+      <c r="F14" s="167"/>
       <c r="G14" s="58">
         <v>88.4</v>
       </c>
@@ -5996,8 +6006,8 @@
       <c r="D15" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="162"/>
-      <c r="F15" s="163"/>
+      <c r="E15" s="166"/>
+      <c r="F15" s="167"/>
       <c r="G15" s="58">
         <v>27.5</v>
       </c>
@@ -6046,8 +6056,8 @@
       <c r="D16" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="162"/>
-      <c r="F16" s="163"/>
+      <c r="E16" s="166"/>
+      <c r="F16" s="167"/>
       <c r="G16" s="58">
         <v>94.8</v>
       </c>
@@ -6096,8 +6106,8 @@
       <c r="D17" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="162"/>
-      <c r="F17" s="163"/>
+      <c r="E17" s="166"/>
+      <c r="F17" s="167"/>
       <c r="G17" s="58">
         <v>861.6</v>
       </c>
@@ -6149,8 +6159,8 @@
       <c r="D18" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="162"/>
-      <c r="F18" s="163"/>
+      <c r="E18" s="166"/>
+      <c r="F18" s="167"/>
       <c r="G18" s="58">
         <v>48.1</v>
       </c>
@@ -6199,8 +6209,8 @@
       <c r="D19" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="E19" s="162"/>
-      <c r="F19" s="163"/>
+      <c r="E19" s="166"/>
+      <c r="F19" s="167"/>
       <c r="G19" s="58">
         <v>41.8</v>
       </c>
@@ -6255,6 +6265,14 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="T1:T2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="N1:P1"/>
     <mergeCell ref="E9:E19"/>
     <mergeCell ref="F9:F19"/>
     <mergeCell ref="B1:B2"/>
@@ -6269,14 +6287,6 @@
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="V2:W2"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="T1:T2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="N1:P1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="M9:M19">
@@ -6310,40 +6320,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="179" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="184" t="s">
+      <c r="B1" s="179" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="179" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="179" t="s">
+      <c r="C1" s="180" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="180" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="179" t="s">
+      <c r="E1" s="180" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="180" t="s">
+      <c r="F1" s="187" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="180"/>
-      <c r="H1" s="173" t="s">
+      <c r="G1" s="187"/>
+      <c r="H1" s="181" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="173"/>
-      <c r="J1" s="174" t="s">
+      <c r="I1" s="181"/>
+      <c r="J1" s="182" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="174"/>
+      <c r="K1" s="182"/>
     </row>
     <row r="2" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="184"/>
-      <c r="B2" s="184"/>
-      <c r="C2" s="179"/>
-      <c r="D2" s="179"/>
-      <c r="E2" s="179"/>
+      <c r="A2" s="179"/>
+      <c r="B2" s="179"/>
+      <c r="C2" s="180"/>
+      <c r="D2" s="180"/>
+      <c r="E2" s="180"/>
       <c r="F2" s="14" t="s">
         <v>7</v>
       </c>
@@ -6364,16 +6374,16 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="175" t="s">
+      <c r="A3" s="183" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="175">
+      <c r="C3" s="183">
         <v>1550</v>
       </c>
-      <c r="D3" s="175" t="s">
+      <c r="D3" s="183" t="s">
         <v>26</v>
       </c>
       <c r="E3" s="13">
@@ -6399,12 +6409,12 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="176"/>
+      <c r="A4" s="184"/>
       <c r="B4" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="176"/>
-      <c r="D4" s="178"/>
+      <c r="C4" s="184"/>
+      <c r="D4" s="186"/>
       <c r="E4" s="18">
         <v>52</v>
       </c>
@@ -6428,11 +6438,11 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="176"/>
+      <c r="A5" s="184"/>
       <c r="B5" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="176"/>
+      <c r="C5" s="184"/>
       <c r="D5" s="19" t="s">
         <v>14</v>
       </c>
@@ -6460,11 +6470,11 @@
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="177"/>
+      <c r="A6" s="185"/>
       <c r="B6" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="177"/>
+      <c r="C6" s="185"/>
       <c r="D6" s="23" t="s">
         <v>15</v>
       </c>
@@ -6492,16 +6502,16 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="181" t="s">
+      <c r="A7" s="176" t="s">
         <v>23</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="181">
+      <c r="C7" s="176">
         <v>1320</v>
       </c>
-      <c r="D7" s="181" t="s">
+      <c r="D7" s="176" t="s">
         <v>24</v>
       </c>
       <c r="E7" s="3">
@@ -6527,12 +6537,12 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8" s="182"/>
+      <c r="A8" s="177"/>
       <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="182"/>
-      <c r="D8" s="183"/>
+      <c r="C8" s="177"/>
+      <c r="D8" s="178"/>
       <c r="E8" s="1">
         <v>100</v>
       </c>
@@ -6556,11 +6566,11 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" s="182"/>
+      <c r="A9" s="177"/>
       <c r="B9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="182"/>
+      <c r="C9" s="177"/>
       <c r="D9" s="2" t="s">
         <v>15</v>
       </c>
@@ -6588,11 +6598,11 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="182"/>
+      <c r="A10" s="177"/>
       <c r="B10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="182"/>
+      <c r="C10" s="177"/>
       <c r="D10" s="2" t="s">
         <v>25</v>
       </c>
@@ -6620,11 +6630,11 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="183"/>
+      <c r="A11" s="178"/>
       <c r="B11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="183"/>
+      <c r="C11" s="178"/>
       <c r="D11" s="2" t="s">
         <v>21</v>
       </c>
@@ -6653,6 +6663,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:G1"/>
     <mergeCell ref="A7:A11"/>
     <mergeCell ref="C7:C11"/>
     <mergeCell ref="D7:D8"/>
@@ -6660,13 +6677,6 @@
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6685,40 +6695,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="179" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="184" t="s">
+      <c r="B1" s="179" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="179" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="179" t="s">
+      <c r="C1" s="180" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="180" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="179" t="s">
+      <c r="E1" s="180" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="180" t="s">
+      <c r="F1" s="187" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="180"/>
-      <c r="H1" s="173" t="s">
+      <c r="G1" s="187"/>
+      <c r="H1" s="181" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="173"/>
-      <c r="J1" s="174" t="s">
+      <c r="I1" s="181"/>
+      <c r="J1" s="182" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="174"/>
+      <c r="K1" s="182"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="184"/>
-      <c r="B2" s="184"/>
-      <c r="C2" s="179"/>
-      <c r="D2" s="179"/>
-      <c r="E2" s="179"/>
+      <c r="A2" s="179"/>
+      <c r="B2" s="179"/>
+      <c r="C2" s="180"/>
+      <c r="D2" s="180"/>
+      <c r="E2" s="180"/>
       <c r="F2" s="14" t="s">
         <v>7</v>
       </c>
@@ -6739,16 +6749,16 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="181" t="s">
+      <c r="A3" s="176" t="s">
         <v>23</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="181">
+      <c r="C3" s="176">
         <v>1320</v>
       </c>
-      <c r="D3" s="181" t="s">
+      <c r="D3" s="176" t="s">
         <v>24</v>
       </c>
       <c r="E3" s="3">
@@ -6774,12 +6784,12 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="182"/>
+      <c r="A4" s="177"/>
       <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="182"/>
-      <c r="D4" s="183"/>
+      <c r="C4" s="177"/>
+      <c r="D4" s="178"/>
       <c r="E4" s="1">
         <v>100</v>
       </c>
@@ -6803,11 +6813,11 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="182"/>
+      <c r="A5" s="177"/>
       <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="182"/>
+      <c r="C5" s="177"/>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
@@ -6835,11 +6845,11 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="182"/>
+      <c r="A6" s="177"/>
       <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="182"/>
+      <c r="C6" s="177"/>
       <c r="D6" s="2" t="s">
         <v>25</v>
       </c>
@@ -6867,11 +6877,11 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="183"/>
+      <c r="A7" s="178"/>
       <c r="B7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="183"/>
+      <c r="C7" s="178"/>
       <c r="D7" s="2" t="s">
         <v>21</v>
       </c>
@@ -6918,116 +6928,120 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D6C66A9-86C5-4B44-B720-CA86E494EFA2}">
-  <dimension ref="A1:V35"/>
+  <dimension ref="A1:W43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" style="32" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5703125" style="35" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" style="38" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.7109375" style="44" customWidth="1"/>
-    <col min="5" max="6" width="7.7109375" style="34" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" style="137" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" style="136" customWidth="1"/>
-    <col min="9" max="9" width="7.28515625" style="91" customWidth="1"/>
-    <col min="10" max="10" width="7.28515625" style="92" customWidth="1"/>
-    <col min="11" max="11" width="7.28515625" style="41" customWidth="1"/>
-    <col min="12" max="13" width="7.28515625" style="92" customWidth="1"/>
-    <col min="14" max="14" width="7.28515625" style="41" customWidth="1"/>
-    <col min="15" max="16" width="7.28515625" style="92" customWidth="1"/>
-    <col min="17" max="17" width="7.28515625" style="41" customWidth="1"/>
-    <col min="18" max="18" width="7.28515625" style="35" customWidth="1"/>
-    <col min="19" max="22" width="7.28515625" style="32" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="32"/>
+    <col min="5" max="7" width="7.7109375" style="34" customWidth="1"/>
+    <col min="8" max="8" width="8.7109375" style="137" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" style="136" customWidth="1"/>
+    <col min="10" max="10" width="7.28515625" style="91" customWidth="1"/>
+    <col min="11" max="11" width="7.28515625" style="92" customWidth="1"/>
+    <col min="12" max="12" width="7.28515625" style="41" customWidth="1"/>
+    <col min="13" max="14" width="7.28515625" style="92" customWidth="1"/>
+    <col min="15" max="15" width="7.28515625" style="41" customWidth="1"/>
+    <col min="16" max="17" width="7.28515625" style="92" customWidth="1"/>
+    <col min="18" max="18" width="7.28515625" style="41" customWidth="1"/>
+    <col min="19" max="19" width="7.28515625" style="35" customWidth="1"/>
+    <col min="20" max="23" width="7.28515625" style="32" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="145" t="s">
+    <row r="1" spans="1:23" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="148" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="153" t="s">
+      <c r="B1" s="150" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="147" t="s">
+      <c r="C1" s="152" t="s">
         <v>121</v>
       </c>
-      <c r="D1" s="140" t="s">
+      <c r="D1" s="145" t="s">
         <v>98</v>
       </c>
-      <c r="E1" s="141" t="s">
+      <c r="E1" s="146" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="151" t="s">
+      <c r="F1" s="146" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="155" t="s">
         <v>115</v>
       </c>
-      <c r="G1" s="143" t="s">
+      <c r="H1" s="141" t="s">
         <v>116</v>
       </c>
-      <c r="H1" s="138" t="s">
+      <c r="I1" s="143" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="140" t="s">
+      <c r="J1" s="145" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="141"/>
-      <c r="K1" s="142"/>
-      <c r="L1" s="140" t="s">
+      <c r="K1" s="146"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="145" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="141"/>
-      <c r="N1" s="142"/>
-      <c r="O1" s="140" t="s">
+      <c r="N1" s="146"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="145" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="141"/>
-      <c r="Q1" s="142"/>
-      <c r="S1" s="128"/>
+      <c r="Q1" s="146"/>
+      <c r="R1" s="147"/>
       <c r="T1" s="128"/>
       <c r="U1" s="128"/>
       <c r="V1" s="128"/>
-    </row>
-    <row r="2" spans="1:22" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="146"/>
-      <c r="B2" s="154"/>
-      <c r="C2" s="148"/>
-      <c r="D2" s="149"/>
-      <c r="E2" s="150"/>
-      <c r="F2" s="152"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="139"/>
-      <c r="I2" s="111" t="s">
+      <c r="W1" s="128"/>
+    </row>
+    <row r="2" spans="1:23" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="149"/>
+      <c r="B2" s="151"/>
+      <c r="C2" s="153"/>
+      <c r="D2" s="157"/>
+      <c r="E2" s="154"/>
+      <c r="F2" s="154"/>
+      <c r="G2" s="156"/>
+      <c r="H2" s="142"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="111" t="s">
         <v>36</v>
       </c>
-      <c r="J2" s="110" t="s">
+      <c r="K2" s="110" t="s">
         <v>37</v>
       </c>
-      <c r="K2" s="51" t="s">
+      <c r="L2" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="L2" s="110" t="s">
+      <c r="M2" s="110" t="s">
         <v>36</v>
       </c>
-      <c r="M2" s="110" t="s">
+      <c r="N2" s="110" t="s">
         <v>37</v>
       </c>
-      <c r="N2" s="52" t="s">
+      <c r="O2" s="52" t="s">
         <v>50</v>
       </c>
-      <c r="O2" s="110" t="s">
+      <c r="P2" s="110" t="s">
         <v>36</v>
       </c>
-      <c r="P2" s="110" t="s">
+      <c r="Q2" s="110" t="s">
         <v>37</v>
       </c>
-      <c r="Q2" s="52" t="s">
+      <c r="R2" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="129"/>
-      <c r="S2" s="127"/>
+      <c r="S2" s="129"/>
       <c r="T2" s="127"/>
       <c r="U2" s="127"/>
       <c r="V2" s="127"/>
-    </row>
-    <row r="3" spans="1:22" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="W2" s="127"/>
+    </row>
+    <row r="3" spans="1:23" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="30">
         <v>1064</v>
       </c>
@@ -7041,53 +7055,54 @@
       <c r="E3" s="31">
         <v>0</v>
       </c>
-      <c r="F3" s="84">
+      <c r="F3" s="31"/>
+      <c r="G3" s="84">
         <v>157.88</v>
       </c>
-      <c r="G3" s="134">
-        <f>F3</f>
+      <c r="H3" s="134">
+        <f>G3</f>
         <v>157.88</v>
       </c>
-      <c r="H3" s="135">
-        <f>F3</f>
+      <c r="I3" s="135">
+        <f>G3</f>
         <v>157.88</v>
       </c>
-      <c r="I3" s="95">
+      <c r="J3" s="95">
         <v>0.93500000000000005</v>
       </c>
-      <c r="J3" s="96">
+      <c r="K3" s="96">
         <v>0.372</v>
       </c>
-      <c r="K3" s="90">
-        <f t="shared" ref="K3:K9" si="0">I3-J3</f>
+      <c r="L3" s="90">
+        <f t="shared" ref="L3:L9" si="0">J3-K3</f>
         <v>0.56300000000000006</v>
       </c>
-      <c r="L3" s="96">
-        <v>0</v>
-      </c>
       <c r="M3" s="96">
+        <v>0</v>
+      </c>
+      <c r="N3" s="96">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="N3" s="90">
-        <f t="shared" ref="N3:N9" si="1">L3-M3</f>
+      <c r="O3" s="90">
+        <f t="shared" ref="O3:O9" si="1">M3-N3</f>
         <v>-1.2999999999999999E-2</v>
       </c>
-      <c r="O3" s="96">
+      <c r="P3" s="96">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="P3" s="96">
+      <c r="Q3" s="96">
         <v>0.61499999999999999</v>
       </c>
-      <c r="Q3" s="90">
-        <f t="shared" ref="Q3:Q9" si="2">O3-P3</f>
+      <c r="R3" s="90">
+        <f t="shared" ref="R3:R9" si="2">P3-Q3</f>
         <v>-0.55000000000000004</v>
       </c>
-      <c r="R3" s="132"/>
-      <c r="S3" s="133" t="s">
+      <c r="S3" s="132"/>
+      <c r="T3" s="133" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:22" s="30" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:23" s="30" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="32" t="s">
         <v>124</v>
       </c>
@@ -7101,50 +7116,51 @@
       <c r="E4" s="31">
         <v>193.08</v>
       </c>
-      <c r="F4" s="84">
+      <c r="F4" s="31"/>
+      <c r="G4" s="84">
         <v>157.9</v>
       </c>
-      <c r="G4" s="134">
+      <c r="H4" s="134">
         <v>157.9</v>
       </c>
-      <c r="H4" s="135">
+      <c r="I4" s="135">
         <v>350.95</v>
       </c>
-      <c r="I4" s="95">
+      <c r="J4" s="95">
         <v>0.95</v>
       </c>
-      <c r="J4" s="96">
+      <c r="K4" s="96">
         <v>0.55800000000000005</v>
       </c>
-      <c r="K4" s="90">
+      <c r="L4" s="90">
         <f t="shared" si="0"/>
         <v>0.3919999999999999</v>
       </c>
-      <c r="L4" s="96">
-        <v>0</v>
-      </c>
       <c r="M4" s="96">
+        <v>0</v>
+      </c>
+      <c r="N4" s="96">
         <v>1.9E-2</v>
       </c>
-      <c r="N4" s="90">
+      <c r="O4" s="90">
         <f t="shared" si="1"/>
         <v>-1.9E-2</v>
       </c>
-      <c r="O4" s="96">
+      <c r="P4" s="96">
         <v>0.05</v>
       </c>
-      <c r="P4" s="96">
+      <c r="Q4" s="96">
         <v>0.42299999999999999</v>
       </c>
-      <c r="Q4" s="90">
+      <c r="R4" s="90">
         <f t="shared" si="2"/>
         <v>-0.373</v>
       </c>
-      <c r="S4" s="130" t="s">
+      <c r="T4" s="130" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:22" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="35"/>
       <c r="C5" s="38" t="s">
         <v>122</v>
@@ -7155,50 +7171,51 @@
       <c r="E5" s="31">
         <v>181.31</v>
       </c>
-      <c r="F5" s="84">
+      <c r="F5" s="31"/>
+      <c r="G5" s="84">
         <v>157.9</v>
       </c>
-      <c r="G5" s="134">
+      <c r="H5" s="134">
         <v>157.9</v>
       </c>
-      <c r="H5" s="135">
+      <c r="I5" s="135">
         <v>339.19</v>
       </c>
-      <c r="I5" s="95">
+      <c r="J5" s="95">
         <v>0.93500000000000005</v>
       </c>
-      <c r="J5" s="96">
+      <c r="K5" s="96">
         <v>0.58399999999999996</v>
       </c>
-      <c r="K5" s="90">
+      <c r="L5" s="90">
         <f t="shared" si="0"/>
         <v>0.35100000000000009</v>
       </c>
-      <c r="L5" s="96">
-        <v>0</v>
-      </c>
       <c r="M5" s="96">
+        <v>0</v>
+      </c>
+      <c r="N5" s="96">
         <v>0.02</v>
       </c>
-      <c r="N5" s="90">
+      <c r="O5" s="90">
         <f t="shared" si="1"/>
         <v>-0.02</v>
       </c>
-      <c r="O5" s="96">
+      <c r="P5" s="96">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="P5" s="96">
+      <c r="Q5" s="96">
         <v>0.39600000000000002</v>
       </c>
-      <c r="Q5" s="90">
+      <c r="R5" s="90">
         <f t="shared" si="2"/>
         <v>-0.33100000000000002</v>
       </c>
-      <c r="S5" s="35" t="s">
+      <c r="T5" s="35" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="6" spans="1:22" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="35"/>
       <c r="C6" s="38" t="s">
         <v>125</v>
@@ -7209,48 +7226,49 @@
       <c r="E6" s="31">
         <v>133.22999999999999</v>
       </c>
-      <c r="F6" s="84">
+      <c r="F6" s="31"/>
+      <c r="G6" s="84">
         <v>78.94</v>
       </c>
-      <c r="G6" s="134">
+      <c r="H6" s="134">
         <v>78.94</v>
       </c>
-      <c r="H6" s="135">
+      <c r="I6" s="135">
         <v>212.17</v>
       </c>
-      <c r="I6" s="95">
+      <c r="J6" s="95">
         <v>0.86699999999999999</v>
       </c>
-      <c r="J6" s="96">
+      <c r="K6" s="96">
         <v>0.71</v>
       </c>
-      <c r="K6" s="90">
+      <c r="L6" s="90">
         <f t="shared" si="0"/>
         <v>0.15700000000000003</v>
       </c>
-      <c r="L6" s="96">
-        <v>0</v>
-      </c>
       <c r="M6" s="96">
+        <v>0</v>
+      </c>
+      <c r="N6" s="96">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="N6" s="90">
+      <c r="O6" s="90">
         <f t="shared" si="1"/>
         <v>-8.9999999999999993E-3</v>
       </c>
-      <c r="O6" s="96">
+      <c r="P6" s="96">
         <v>0.13300000000000001</v>
       </c>
-      <c r="P6" s="96">
+      <c r="Q6" s="96">
         <v>0.28000000000000003</v>
       </c>
-      <c r="Q6" s="90">
+      <c r="R6" s="90">
         <f t="shared" si="2"/>
         <v>-0.14700000000000002</v>
       </c>
-      <c r="S6" s="131"/>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="T6" s="131"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C7" s="81" t="s">
         <v>105</v>
       </c>
@@ -7260,50 +7278,50 @@
       <c r="E7" s="34">
         <v>0</v>
       </c>
-      <c r="F7" s="84">
+      <c r="G7" s="84">
         <v>78.94</v>
       </c>
-      <c r="G7" s="134">
-        <f t="shared" ref="G7:G17" si="3">F7</f>
+      <c r="H7" s="134">
+        <f t="shared" ref="H7:H17" si="3">G7</f>
         <v>78.94</v>
       </c>
-      <c r="H7" s="136">
-        <f>D7+F7</f>
+      <c r="I7" s="136">
+        <f>D7+G7</f>
         <v>194.11</v>
       </c>
-      <c r="I7" s="91">
+      <c r="J7" s="91">
         <v>0.93300000000000005</v>
       </c>
-      <c r="J7" s="92">
+      <c r="K7" s="92">
         <v>0.76900000000000002</v>
       </c>
-      <c r="K7" s="90">
+      <c r="L7" s="90">
         <f t="shared" si="0"/>
         <v>0.16400000000000003</v>
       </c>
-      <c r="L7" s="92">
-        <v>0</v>
-      </c>
       <c r="M7" s="92">
+        <v>0</v>
+      </c>
+      <c r="N7" s="92">
         <v>0.01</v>
       </c>
-      <c r="N7" s="90">
+      <c r="O7" s="90">
         <f t="shared" si="1"/>
         <v>-0.01</v>
       </c>
-      <c r="O7" s="92">
+      <c r="P7" s="92">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="P7" s="92">
+      <c r="Q7" s="92">
         <v>0.221</v>
       </c>
-      <c r="Q7" s="90">
+      <c r="R7" s="90">
         <f t="shared" si="2"/>
         <v>-0.154</v>
       </c>
-      <c r="S7" s="35"/>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="T7" s="35"/>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B8" s="71" t="s">
         <v>106</v>
       </c>
@@ -7316,49 +7334,49 @@
       <c r="E8" s="34">
         <v>0</v>
       </c>
-      <c r="F8" s="84">
+      <c r="G8" s="84">
         <v>32.880000000000003</v>
       </c>
-      <c r="G8" s="134">
+      <c r="H8" s="134">
         <f t="shared" si="3"/>
         <v>32.880000000000003</v>
       </c>
-      <c r="H8" s="136">
-        <f>D8+F8</f>
+      <c r="I8" s="136">
+        <f>D8+G8</f>
         <v>194.95</v>
       </c>
-      <c r="I8" s="91">
+      <c r="J8" s="91">
         <v>0.96599999999999997</v>
       </c>
-      <c r="J8" s="92">
+      <c r="K8" s="92">
         <v>0.82799999999999996</v>
       </c>
-      <c r="K8" s="90">
-        <f>I8-J8</f>
+      <c r="L8" s="90">
+        <f>J8-K8</f>
         <v>0.13800000000000001</v>
       </c>
-      <c r="L8" s="92">
-        <v>0</v>
-      </c>
       <c r="M8" s="92">
+        <v>0</v>
+      </c>
+      <c r="N8" s="92">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="N8" s="90">
-        <f>L8-M8</f>
+      <c r="O8" s="90">
+        <f>M8-N8</f>
         <v>-8.0000000000000004E-4</v>
       </c>
-      <c r="O8" s="92">
+      <c r="P8" s="92">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="P8" s="92">
+      <c r="Q8" s="92">
         <v>0.16400000000000001</v>
       </c>
-      <c r="Q8" s="90">
-        <f>O8-P8</f>
+      <c r="R8" s="90">
+        <f>P8-Q8</f>
         <v>-0.13</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B9" s="71" t="s">
         <v>106</v>
       </c>
@@ -7371,58 +7389,58 @@
       <c r="E9" s="34">
         <v>0</v>
       </c>
-      <c r="F9" s="84">
+      <c r="G9" s="84">
         <v>68.260000000000005</v>
       </c>
-      <c r="G9" s="134">
+      <c r="H9" s="134">
         <f t="shared" si="3"/>
         <v>68.260000000000005</v>
       </c>
-      <c r="H9" s="136">
-        <f>D9+F9</f>
+      <c r="I9" s="136">
+        <f>D9+G9</f>
         <v>193.26</v>
       </c>
-      <c r="I9" s="91">
+      <c r="J9" s="91">
         <v>0.93600000000000005</v>
       </c>
-      <c r="J9" s="92">
+      <c r="K9" s="92">
         <v>0.73799999999999999</v>
       </c>
-      <c r="K9" s="90">
+      <c r="L9" s="90">
         <f t="shared" si="0"/>
         <v>0.19800000000000006</v>
       </c>
-      <c r="L9" s="92">
-        <v>0</v>
-      </c>
       <c r="M9" s="92">
+        <v>0</v>
+      </c>
+      <c r="N9" s="92">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="N9" s="90">
+      <c r="O9" s="90">
         <f t="shared" si="1"/>
         <v>-8.9999999999999993E-3</v>
       </c>
-      <c r="O9" s="92">
+      <c r="P9" s="92">
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="P9" s="92">
+      <c r="Q9" s="92">
         <v>0.252</v>
       </c>
-      <c r="Q9" s="90">
+      <c r="R9" s="90">
         <f t="shared" si="2"/>
         <v>-0.188</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B10" s="71"/>
       <c r="D10" s="126"/>
-      <c r="F10" s="84"/>
-      <c r="G10" s="134"/>
-      <c r="K10" s="90"/>
-      <c r="N10" s="90"/>
-      <c r="Q10" s="90"/>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="G10" s="84"/>
+      <c r="H10" s="134"/>
+      <c r="L10" s="90"/>
+      <c r="O10" s="90"/>
+      <c r="R10" s="90"/>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C11" s="81" t="s">
         <v>126</v>
       </c>
@@ -7432,47 +7450,47 @@
       <c r="E11" s="34">
         <v>386.15</v>
       </c>
-      <c r="F11" s="34">
+      <c r="G11" s="34">
         <v>78.900000000000006</v>
       </c>
-      <c r="G11" s="137">
+      <c r="H11" s="137">
         <v>78.900000000000006</v>
       </c>
-      <c r="H11" s="136">
+      <c r="I11" s="136">
         <v>580.26</v>
       </c>
-      <c r="I11" s="91">
+      <c r="J11" s="91">
         <v>0.93300000000000005</v>
       </c>
-      <c r="J11" s="92">
+      <c r="K11" s="92">
         <v>0.76900000000000002</v>
       </c>
-      <c r="K11" s="90">
-        <f>I11-J11</f>
+      <c r="L11" s="90">
+        <f>J11-K11</f>
         <v>0.16400000000000003</v>
       </c>
-      <c r="L11" s="92">
-        <v>0</v>
-      </c>
       <c r="M11" s="92">
+        <v>0</v>
+      </c>
+      <c r="N11" s="92">
         <v>0.01</v>
       </c>
-      <c r="N11" s="90">
-        <f>L11-M11</f>
+      <c r="O11" s="90">
+        <f>M11-N11</f>
         <v>-0.01</v>
       </c>
-      <c r="O11" s="92">
+      <c r="P11" s="92">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="P11" s="92">
+      <c r="Q11" s="92">
         <v>0.22</v>
       </c>
-      <c r="Q11" s="90">
-        <f>O11-P11</f>
+      <c r="R11" s="90">
+        <f>P11-Q11</f>
         <v>-0.153</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C12" s="38" t="s">
         <v>104</v>
       </c>
@@ -7482,54 +7500,54 @@
       <c r="E12" s="34">
         <v>115.17</v>
       </c>
-      <c r="F12" s="84">
+      <c r="G12" s="84">
         <v>78.94</v>
       </c>
-      <c r="G12" s="134">
-        <f>F12</f>
+      <c r="H12" s="134">
+        <f>G12</f>
         <v>78.94</v>
       </c>
-      <c r="H12" s="136">
-        <f>SUM(D12:F12)</f>
+      <c r="I12" s="136">
+        <f>SUM(D12:G12)</f>
         <v>343.75</v>
       </c>
-      <c r="I12" s="91">
+      <c r="J12" s="91">
         <v>0.93500000000000005</v>
       </c>
-      <c r="J12" s="92">
+      <c r="K12" s="92">
         <v>0.76900000000000002</v>
       </c>
-      <c r="K12" s="90">
-        <f>I12-J12</f>
+      <c r="L12" s="90">
+        <f>J12-K12</f>
         <v>0.16600000000000004</v>
       </c>
-      <c r="L12" s="92">
-        <v>0</v>
-      </c>
       <c r="M12" s="92">
+        <v>0</v>
+      </c>
+      <c r="N12" s="92">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="N12" s="90">
-        <f>L12-M12</f>
+      <c r="O12" s="90">
+        <f>M12-N12</f>
         <v>-1.0999999999999999E-2</v>
       </c>
-      <c r="O12" s="92">
+      <c r="P12" s="92">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="P12" s="92">
+      <c r="Q12" s="92">
         <v>0.221</v>
       </c>
-      <c r="Q12" s="90">
-        <f>O12-P12</f>
+      <c r="R12" s="90">
+        <f>P12-Q12</f>
         <v>-0.154</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="30"/>
-      <c r="F13" s="84"/>
-      <c r="G13" s="134"/>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="G13" s="84"/>
+      <c r="H13" s="134"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B14" s="35" t="s">
         <v>100</v>
       </c>
@@ -7542,49 +7560,49 @@
       <c r="E14" s="34">
         <v>193.08</v>
       </c>
-      <c r="F14" s="84">
+      <c r="G14" s="84">
         <v>157.88</v>
       </c>
-      <c r="G14" s="134">
+      <c r="H14" s="134">
         <f t="shared" si="3"/>
         <v>157.88</v>
       </c>
-      <c r="H14" s="136">
-        <f>SUM(D14:F14)</f>
+      <c r="I14" s="136">
+        <f>SUM(D14:G14)</f>
         <v>532.27</v>
       </c>
-      <c r="I14" s="91">
+      <c r="J14" s="91">
         <v>0.95</v>
       </c>
-      <c r="J14" s="92">
+      <c r="K14" s="92">
         <v>0.55800000000000005</v>
       </c>
-      <c r="K14" s="90">
-        <f>I14-J14</f>
+      <c r="L14" s="90">
+        <f>J14-K14</f>
         <v>0.3919999999999999</v>
       </c>
-      <c r="L14" s="92">
-        <v>0</v>
-      </c>
       <c r="M14" s="92">
+        <v>0</v>
+      </c>
+      <c r="N14" s="92">
         <v>1.9E-2</v>
       </c>
-      <c r="N14" s="90">
-        <f>L14-M14</f>
+      <c r="O14" s="90">
+        <f>M14-N14</f>
         <v>-1.9E-2</v>
       </c>
-      <c r="O14" s="92">
+      <c r="P14" s="92">
         <v>0.05</v>
       </c>
-      <c r="P14" s="92">
+      <c r="Q14" s="92">
         <v>0.42299999999999999</v>
       </c>
-      <c r="Q14" s="90">
-        <f>O14-P14</f>
+      <c r="R14" s="90">
+        <f>P14-Q14</f>
         <v>-0.373</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="30"/>
       <c r="B15" s="35" t="s">
         <v>100</v>
@@ -7598,50 +7616,50 @@
       <c r="E15" s="34">
         <v>193.08</v>
       </c>
-      <c r="F15" s="84">
-        <f>F14</f>
+      <c r="G15" s="84">
+        <f>G14</f>
         <v>157.88</v>
       </c>
-      <c r="G15" s="134">
+      <c r="H15" s="134">
         <f t="shared" si="3"/>
         <v>157.88</v>
       </c>
-      <c r="H15" s="136">
-        <f>SUM(D15:F15)</f>
+      <c r="I15" s="136">
+        <f>SUM(D15:G15)</f>
         <v>515.51</v>
       </c>
-      <c r="I15" s="91">
+      <c r="J15" s="91">
         <v>0.96599999999999997</v>
       </c>
-      <c r="J15" s="92">
+      <c r="K15" s="92">
         <v>0.627</v>
       </c>
-      <c r="K15" s="90">
-        <f>I15-J15</f>
+      <c r="L15" s="90">
+        <f>J15-K15</f>
         <v>0.33899999999999997</v>
       </c>
-      <c r="L15" s="92">
-        <v>0</v>
-      </c>
       <c r="M15" s="92">
+        <v>0</v>
+      </c>
+      <c r="N15" s="92">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="N15" s="90">
-        <f>L15-M15</f>
+      <c r="O15" s="90">
+        <f>M15-N15</f>
         <v>-1.7999999999999999E-2</v>
       </c>
-      <c r="O15" s="92">
+      <c r="P15" s="92">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="P15" s="92">
+      <c r="Q15" s="92">
         <v>0.35399999999999998</v>
       </c>
-      <c r="Q15" s="90">
-        <f>O15-P15</f>
+      <c r="R15" s="90">
+        <f>P15-Q15</f>
         <v>-0.31999999999999995</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B16" s="35" t="s">
         <v>100</v>
       </c>
@@ -7654,50 +7672,50 @@
       <c r="E16" s="34">
         <v>164.55</v>
       </c>
-      <c r="F16" s="84">
-        <f t="shared" ref="F16:F17" si="4">F15</f>
+      <c r="G16" s="84">
+        <f t="shared" ref="G16:G17" si="4">G15</f>
         <v>157.88</v>
       </c>
-      <c r="G16" s="134">
+      <c r="H16" s="134">
         <f t="shared" si="3"/>
         <v>157.88</v>
       </c>
-      <c r="H16" s="136">
-        <f>SUM(D16:F16)</f>
+      <c r="I16" s="136">
+        <f>SUM(D16:G16)</f>
         <v>455.65999999999997</v>
       </c>
-      <c r="I16" s="91">
+      <c r="J16" s="91">
         <v>0.96599999999999997</v>
       </c>
-      <c r="J16" s="92">
+      <c r="K16" s="92">
         <v>0.83299999999999996</v>
       </c>
-      <c r="K16" s="90">
-        <f>I16-J16</f>
+      <c r="L16" s="90">
+        <f>J16-K16</f>
         <v>0.13300000000000001</v>
       </c>
-      <c r="L16" s="92">
-        <v>0</v>
-      </c>
       <c r="M16" s="92">
+        <v>0</v>
+      </c>
+      <c r="N16" s="92">
         <v>1.9E-2</v>
       </c>
-      <c r="N16" s="90">
-        <f>L16-M16</f>
+      <c r="O16" s="90">
+        <f>M16-N16</f>
         <v>-1.9E-2</v>
       </c>
-      <c r="O16" s="92">
+      <c r="P16" s="92">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="P16" s="92">
+      <c r="Q16" s="92">
         <v>0.14799999999999999</v>
       </c>
-      <c r="Q16" s="90">
-        <f>O16-P16</f>
+      <c r="R16" s="90">
+        <f>P16-Q16</f>
         <v>-0.11399999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B17" s="35" t="s">
         <v>100</v>
       </c>
@@ -7710,55 +7728,55 @@
       <c r="E17" s="34">
         <v>133.22999999999999</v>
       </c>
-      <c r="F17" s="84">
+      <c r="G17" s="84">
         <f t="shared" si="4"/>
         <v>157.88</v>
       </c>
-      <c r="G17" s="134">
+      <c r="H17" s="134">
         <f t="shared" si="3"/>
         <v>157.88</v>
       </c>
-      <c r="H17" s="136">
-        <f>SUM(D17:F17)</f>
+      <c r="I17" s="136">
+        <f>SUM(D17:G17)</f>
         <v>406.28</v>
       </c>
-      <c r="I17" s="91">
+      <c r="J17" s="91">
         <v>0.96499999999999997</v>
       </c>
-      <c r="J17" s="92">
+      <c r="K17" s="92">
         <v>0.94099999999999995</v>
       </c>
-      <c r="K17" s="90">
-        <f>I17-J17</f>
+      <c r="L17" s="90">
+        <f>J17-K17</f>
         <v>2.4000000000000021E-2</v>
       </c>
-      <c r="L17" s="92">
-        <v>0</v>
-      </c>
       <c r="M17" s="92">
+        <v>0</v>
+      </c>
+      <c r="N17" s="92">
         <v>1.9E-2</v>
       </c>
-      <c r="N17" s="90">
-        <f>L17-M17</f>
+      <c r="O17" s="90">
+        <f>M17-N17</f>
         <v>-1.9E-2</v>
       </c>
-      <c r="O17" s="92">
+      <c r="P17" s="92">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="P17" s="92">
+      <c r="Q17" s="92">
         <v>0.04</v>
       </c>
-      <c r="Q17" s="90">
-        <f>O17-P17</f>
+      <c r="R17" s="90">
+        <f>P17-Q17</f>
         <v>-4.9999999999999975E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="K18" s="90"/>
-      <c r="N18" s="90"/>
-      <c r="Q18" s="90"/>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L18" s="90"/>
+      <c r="O18" s="90"/>
+      <c r="R18" s="90"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="32">
         <v>750</v>
       </c>
@@ -7774,48 +7792,48 @@
       <c r="E19" s="34">
         <v>135.84</v>
       </c>
-      <c r="F19" s="34">
+      <c r="G19" s="34">
         <v>49.49</v>
       </c>
-      <c r="G19" s="137">
-        <f>F19</f>
+      <c r="H19" s="137">
+        <f>G19</f>
         <v>49.49</v>
       </c>
-      <c r="H19" s="136">
+      <c r="I19" s="136">
         <v>185.33</v>
       </c>
-      <c r="I19" s="91">
+      <c r="J19" s="91">
         <v>0.93300000000000005</v>
       </c>
-      <c r="J19" s="92">
+      <c r="K19" s="92">
         <v>0.501</v>
       </c>
-      <c r="K19" s="90">
-        <f t="shared" ref="K19:K22" si="5">I19-J19</f>
+      <c r="L19" s="90">
+        <f t="shared" ref="L19:L22" si="5">J19-K19</f>
         <v>0.43200000000000005</v>
       </c>
-      <c r="L19" s="92">
-        <v>0</v>
-      </c>
       <c r="M19" s="92">
+        <v>0</v>
+      </c>
+      <c r="N19" s="92">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="N19" s="90">
-        <f t="shared" ref="N19:N22" si="6">L19-M19</f>
+      <c r="O19" s="90">
+        <f t="shared" ref="O19:O22" si="6">M19-N19</f>
         <v>-1.4999999999999999E-2</v>
       </c>
-      <c r="O19" s="92">
+      <c r="P19" s="92">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="P19" s="92">
+      <c r="Q19" s="92">
         <v>0.48399999999999999</v>
       </c>
-      <c r="Q19" s="90">
-        <f t="shared" ref="Q19:Q22" si="7">O19-P19</f>
+      <c r="R19" s="90">
+        <f t="shared" ref="R19:R22" si="7">P19-Q19</f>
         <v>-0.41699999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B20" s="35" t="s">
         <v>137</v>
       </c>
@@ -7828,47 +7846,47 @@
       <c r="E20" s="34">
         <v>135.84</v>
       </c>
-      <c r="F20" s="34">
+      <c r="G20" s="34">
         <v>49.49</v>
       </c>
-      <c r="G20" s="137">
+      <c r="H20" s="137">
         <v>98.99</v>
       </c>
-      <c r="H20" s="136">
+      <c r="I20" s="136">
         <v>370.67</v>
       </c>
-      <c r="I20" s="91">
+      <c r="J20" s="91">
         <v>0.93100000000000005</v>
       </c>
-      <c r="J20" s="92">
+      <c r="K20" s="92">
         <v>0.13300000000000001</v>
       </c>
-      <c r="K20" s="90">
+      <c r="L20" s="90">
         <f t="shared" si="5"/>
         <v>0.79800000000000004</v>
       </c>
-      <c r="L20" s="92">
-        <v>0</v>
-      </c>
       <c r="M20" s="92">
+        <v>0</v>
+      </c>
+      <c r="N20" s="92">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="N20" s="90">
+      <c r="O20" s="90">
         <f t="shared" si="6"/>
         <v>-1.7999999999999999E-2</v>
       </c>
-      <c r="O20" s="92">
+      <c r="P20" s="92">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="P20" s="92">
+      <c r="Q20" s="92">
         <v>0.84799999999999998</v>
       </c>
-      <c r="Q20" s="90">
+      <c r="R20" s="90">
         <f t="shared" si="7"/>
         <v>-0.77899999999999991</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B21" s="35" t="s">
         <v>137</v>
       </c>
@@ -7881,48 +7899,48 @@
       <c r="E21" s="34">
         <v>135.84</v>
       </c>
-      <c r="F21" s="34">
+      <c r="G21" s="34">
         <v>49.49</v>
       </c>
-      <c r="G21" s="137">
-        <f>F21*3</f>
+      <c r="H21" s="137">
+        <f>G21*3</f>
         <v>148.47</v>
       </c>
-      <c r="H21" s="136">
+      <c r="I21" s="136">
         <v>556</v>
       </c>
-      <c r="I21" s="91">
+      <c r="J21" s="91">
         <v>0.93</v>
       </c>
-      <c r="J21" s="92">
+      <c r="K21" s="92">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="K21" s="90">
+      <c r="L21" s="90">
         <f t="shared" si="5"/>
         <v>0.90100000000000002</v>
       </c>
-      <c r="L21" s="92">
-        <v>0</v>
-      </c>
       <c r="M21" s="92">
+        <v>0</v>
+      </c>
+      <c r="N21" s="92">
         <v>1.9E-2</v>
       </c>
-      <c r="N21" s="90">
+      <c r="O21" s="90">
         <f t="shared" si="6"/>
         <v>-1.9E-2</v>
       </c>
-      <c r="O21" s="92">
+      <c r="P21" s="92">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="P21" s="92">
+      <c r="Q21" s="92">
         <v>0.95199999999999996</v>
       </c>
-      <c r="Q21" s="90">
+      <c r="R21" s="90">
         <f t="shared" si="7"/>
         <v>-0.8819999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B22" s="35" t="s">
         <v>137</v>
       </c>
@@ -7935,48 +7953,48 @@
       <c r="E22" s="34">
         <v>135.80000000000001</v>
       </c>
-      <c r="F22" s="34">
+      <c r="G22" s="34">
         <v>49.49</v>
       </c>
-      <c r="G22" s="137">
-        <f>F22*4</f>
+      <c r="H22" s="137">
+        <f>G22*4</f>
         <v>197.96</v>
       </c>
-      <c r="H22" s="136">
+      <c r="I22" s="136">
         <v>741.33</v>
       </c>
-      <c r="I22" s="91">
+      <c r="J22" s="91">
         <v>0.93300000000000005</v>
       </c>
-      <c r="J22" s="92">
+      <c r="K22" s="92">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="K22" s="90">
+      <c r="L22" s="90">
         <f t="shared" si="5"/>
         <v>0.92700000000000005</v>
       </c>
-      <c r="L22" s="92">
-        <v>0</v>
-      </c>
       <c r="M22" s="92">
+        <v>0</v>
+      </c>
+      <c r="N22" s="92">
         <v>1.9E-2</v>
       </c>
-      <c r="N22" s="42">
+      <c r="O22" s="42">
         <f t="shared" si="6"/>
         <v>-1.9E-2</v>
       </c>
-      <c r="O22" s="92">
+      <c r="P22" s="92">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="P22" s="92">
+      <c r="Q22" s="92">
         <v>0.97499999999999998</v>
       </c>
-      <c r="Q22" s="42">
+      <c r="R22" s="42">
         <f t="shared" si="7"/>
         <v>-0.90799999999999992</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B23" s="35" t="s">
         <v>137</v>
       </c>
@@ -7989,48 +8007,48 @@
       <c r="E23" s="34">
         <v>135.80000000000001</v>
       </c>
-      <c r="F23" s="34">
+      <c r="G23" s="34">
         <v>49.49</v>
       </c>
-      <c r="G23" s="137">
-        <f>F23*5</f>
+      <c r="H23" s="137">
+        <f>G23*5</f>
         <v>247.45000000000002</v>
       </c>
-      <c r="H23" s="136">
+      <c r="I23" s="136">
         <v>926.67</v>
       </c>
-      <c r="I23" s="91">
+      <c r="J23" s="91">
         <v>0.93500000000000005</v>
       </c>
-      <c r="J23" s="92">
+      <c r="K23" s="92">
         <v>1E-3</v>
       </c>
-      <c r="K23" s="90">
-        <f t="shared" ref="K23:K25" si="8">I23-J23</f>
+      <c r="L23" s="90">
+        <f t="shared" ref="L23" si="8">J23-K23</f>
         <v>0.93400000000000005</v>
-      </c>
-      <c r="L23" s="92">
-        <v>1.9E-2</v>
       </c>
       <c r="M23" s="92">
         <v>1.9E-2</v>
       </c>
-      <c r="N23" s="42">
-        <f t="shared" ref="N23:N25" si="9">L23-M23</f>
-        <v>0</v>
-      </c>
-      <c r="O23" s="92">
+      <c r="N23" s="92">
+        <v>1.9E-2</v>
+      </c>
+      <c r="O23" s="42">
+        <f t="shared" ref="O23" si="9">M23-N23</f>
+        <v>0</v>
+      </c>
+      <c r="P23" s="92">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="P23" s="92">
+      <c r="Q23" s="92">
         <v>0.98</v>
       </c>
-      <c r="Q23" s="42">
-        <f t="shared" ref="Q23:Q25" si="10">O23-P23</f>
+      <c r="R23" s="42">
+        <f t="shared" ref="R23" si="10">P23-Q23</f>
         <v>-0.91500000000000004</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B24" s="35" t="s">
         <v>137</v>
       </c>
@@ -8043,48 +8061,48 @@
       <c r="E24" s="34">
         <v>135.84</v>
       </c>
-      <c r="F24" s="34">
+      <c r="G24" s="34">
         <v>49.49</v>
       </c>
-      <c r="G24" s="137">
-        <f>F24*6</f>
+      <c r="H24" s="137">
+        <f>G24*6</f>
         <v>296.94</v>
       </c>
-      <c r="H24" s="136">
+      <c r="I24" s="136">
         <v>1112</v>
       </c>
-      <c r="I24" s="91">
+      <c r="J24" s="91">
         <v>0.93300000000000005</v>
       </c>
-      <c r="J24" s="92">
-        <v>0</v>
-      </c>
-      <c r="K24" s="90">
-        <f>I24-J24</f>
+      <c r="K24" s="92">
+        <v>0</v>
+      </c>
+      <c r="L24" s="90">
+        <f>J24-K24</f>
         <v>0.93300000000000005</v>
       </c>
-      <c r="L24" s="92">
-        <v>0</v>
-      </c>
       <c r="M24" s="92">
+        <v>0</v>
+      </c>
+      <c r="N24" s="92">
         <v>1.9E-2</v>
       </c>
-      <c r="N24" s="90">
-        <f>L24-M24</f>
+      <c r="O24" s="90">
+        <f>M24-N24</f>
         <v>-1.9E-2</v>
       </c>
-      <c r="O24" s="92">
+      <c r="P24" s="92">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="P24" s="92">
+      <c r="Q24" s="92">
         <v>0.98099999999999998</v>
       </c>
-      <c r="Q24" s="90">
-        <f>O24-P24</f>
+      <c r="R24" s="90">
+        <f>P24-Q24</f>
         <v>-0.91399999999999992</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B25" s="35" t="s">
         <v>137</v>
       </c>
@@ -8097,172 +8115,447 @@
       <c r="E25" s="34">
         <v>135.84</v>
       </c>
-      <c r="F25" s="34">
+      <c r="G25" s="34">
         <v>49.49</v>
       </c>
-      <c r="G25" s="137">
-        <f>F25*8</f>
+      <c r="H25" s="137">
+        <f>G25*8</f>
         <v>395.92</v>
       </c>
-      <c r="H25" s="136">
+      <c r="I25" s="136">
         <v>1482.67</v>
       </c>
-      <c r="I25" s="91">
+      <c r="J25" s="91">
         <v>0.93</v>
       </c>
-      <c r="J25" s="92">
-        <v>0</v>
-      </c>
-      <c r="K25" s="90">
-        <f>I25-J25</f>
+      <c r="K25" s="92">
+        <v>0</v>
+      </c>
+      <c r="L25" s="90">
+        <f>J25-K25</f>
         <v>0.93</v>
       </c>
-      <c r="L25" s="92">
-        <v>0</v>
-      </c>
       <c r="M25" s="92">
+        <v>0</v>
+      </c>
+      <c r="N25" s="92">
         <v>1.9E-2</v>
       </c>
-      <c r="N25" s="90">
-        <f>L25-M25</f>
+      <c r="O25" s="90">
+        <f>M25-N25</f>
         <v>-1.9E-2</v>
       </c>
-      <c r="O25" s="92">
+      <c r="P25" s="92">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="P25" s="92">
+      <c r="Q25" s="92">
         <v>0.98099999999999998</v>
       </c>
-      <c r="Q25" s="90">
-        <f>O25-P25</f>
+      <c r="R25" s="90">
+        <f>P25-Q25</f>
         <v>-0.91100000000000003</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="K26" s="97"/>
-      <c r="N26" s="97"/>
-      <c r="Q26" s="97"/>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="191" t="s">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L26" s="90"/>
+      <c r="O26" s="90"/>
+      <c r="R26" s="90"/>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" s="32">
+        <v>1064</v>
+      </c>
+      <c r="B27" s="35" t="s">
+        <v>158</v>
+      </c>
+      <c r="C27" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="D27" s="44">
+        <v>115.17</v>
+      </c>
+      <c r="E27" s="34">
+        <v>181.31</v>
+      </c>
+      <c r="G27" s="34">
+        <v>99.9</v>
+      </c>
+      <c r="H27" s="137">
+        <f>G27</f>
+        <v>99.9</v>
+      </c>
+      <c r="I27" s="136">
+        <v>808.02</v>
+      </c>
+      <c r="J27" s="91">
+        <v>0.93500000000000005</v>
+      </c>
+      <c r="K27" s="92">
+        <v>0.51200000000000001</v>
+      </c>
+      <c r="L27" s="90">
+        <f t="shared" ref="L26:L31" si="11">J27-K27</f>
+        <v>0.42300000000000004</v>
+      </c>
+      <c r="M27" s="92">
+        <v>0</v>
+      </c>
+      <c r="N27" s="92">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="O27" s="90">
+        <f t="shared" ref="O26:O31" si="12">M27-N27</f>
+        <v>-1.2999999999999999E-2</v>
+      </c>
+      <c r="P27" s="92">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="Q27" s="92">
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="R27" s="90">
+        <f t="shared" ref="R26:R31" si="13">P27-Q27</f>
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="35" t="s">
+        <v>159</v>
+      </c>
+      <c r="C28" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="D28" s="44">
+        <v>115.17</v>
+      </c>
+      <c r="E28" s="34">
+        <v>181.31</v>
+      </c>
+      <c r="G28" s="34">
+        <v>100</v>
+      </c>
+      <c r="H28" s="137">
+        <f>G28</f>
+        <v>100</v>
+      </c>
+      <c r="I28" s="136">
+        <v>1104.5999999999999</v>
+      </c>
+      <c r="J28" s="91">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="K28" s="92">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="L28" s="90">
+        <f t="shared" si="11"/>
+        <v>0.624</v>
+      </c>
+      <c r="M28" s="92">
+        <v>0</v>
+      </c>
+      <c r="N28" s="92">
+        <v>1.6E-2</v>
+      </c>
+      <c r="O28" s="90">
+        <f t="shared" si="12"/>
+        <v>-1.6E-2</v>
+      </c>
+      <c r="P28" s="92">
+        <v>0.105</v>
+      </c>
+      <c r="Q28" s="92">
+        <v>0.71299999999999997</v>
+      </c>
+      <c r="R28" s="90">
+        <f t="shared" si="13"/>
+        <v>-0.60799999999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" s="35" t="s">
+        <v>161</v>
+      </c>
+      <c r="C29" s="38" t="s">
+        <v>164</v>
+      </c>
+      <c r="D29" s="44">
+        <v>115.17</v>
+      </c>
+      <c r="E29" s="34">
+        <v>181.31</v>
+      </c>
+      <c r="F29" s="34">
+        <v>75.7</v>
+      </c>
+      <c r="G29" s="34">
+        <v>31.6</v>
+      </c>
+      <c r="H29" s="137">
+        <f>G29</f>
+        <v>31.6</v>
+      </c>
+      <c r="I29" s="136">
+        <v>815.3</v>
+      </c>
+      <c r="J29" s="91">
+        <v>0.96599999999999997</v>
+      </c>
+      <c r="K29" s="92">
+        <v>0.83699999999999997</v>
+      </c>
+      <c r="L29" s="90">
+        <f t="shared" si="11"/>
+        <v>0.129</v>
+      </c>
+      <c r="M29" s="92">
+        <v>0</v>
+      </c>
+      <c r="N29" s="92">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="O29" s="90">
+        <f t="shared" si="12"/>
+        <v>-8.0000000000000002E-3</v>
+      </c>
+      <c r="P29" s="92">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="Q29" s="92">
+        <v>0.155</v>
+      </c>
+      <c r="R29" s="90">
+        <f t="shared" si="13"/>
+        <v>-0.121</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" s="35" t="s">
+        <v>138</v>
+      </c>
+      <c r="C30" s="38" t="s">
+        <v>163</v>
+      </c>
+      <c r="D30" s="44">
+        <v>115.17</v>
+      </c>
+      <c r="E30" s="34">
+        <v>181.31</v>
+      </c>
+      <c r="F30" s="34">
+        <v>74.8</v>
+      </c>
+      <c r="G30" s="34">
+        <v>31.9</v>
+      </c>
+      <c r="H30" s="137">
+        <f>G30</f>
+        <v>31.9</v>
+      </c>
+      <c r="I30" s="136">
+        <v>1454.83</v>
+      </c>
+      <c r="J30" s="91">
+        <v>0.96599999999999997</v>
+      </c>
+      <c r="K30" s="92">
+        <v>0.498</v>
+      </c>
+      <c r="L30" s="90">
+        <f t="shared" si="11"/>
+        <v>0.46799999999999997</v>
+      </c>
+      <c r="M30" s="92">
+        <v>0</v>
+      </c>
+      <c r="N30" s="92">
+        <v>1.2E-2</v>
+      </c>
+      <c r="O30" s="90">
+        <f t="shared" si="12"/>
+        <v>-1.2E-2</v>
+      </c>
+      <c r="P30" s="92">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="Q30" s="92">
+        <v>0.49</v>
+      </c>
+      <c r="R30" s="90">
+        <f t="shared" si="13"/>
+        <v>-0.45599999999999996</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C31" s="81" t="s">
+        <v>165</v>
+      </c>
+      <c r="D31" s="44">
+        <v>115.17</v>
+      </c>
+      <c r="E31" s="34">
+        <v>181.31</v>
+      </c>
+      <c r="F31" s="34">
+        <v>74.7</v>
+      </c>
+      <c r="G31" s="34">
+        <v>32</v>
+      </c>
+      <c r="H31" s="137">
+        <f>G31</f>
+        <v>32</v>
+      </c>
+      <c r="I31" s="136">
+        <v>2071.3200000000002</v>
+      </c>
+      <c r="J31" s="91">
+        <v>0.96499999999999997</v>
+      </c>
+      <c r="K31" s="92">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="L31" s="90">
+        <f t="shared" si="11"/>
+        <v>0.84799999999999998</v>
+      </c>
+      <c r="M31" s="92">
+        <v>0</v>
+      </c>
+      <c r="N31" s="92">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="O31" s="90">
+        <f t="shared" si="12"/>
+        <v>-7.0000000000000001E-3</v>
+      </c>
+      <c r="P31" s="92">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="Q31" s="92">
+        <v>0.875</v>
+      </c>
+      <c r="R31" s="90">
+        <f t="shared" si="13"/>
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="140" t="s">
         <v>113</v>
       </c>
-      <c r="B27" s="69" t="s">
+      <c r="B35" s="69" t="s">
         <v>82</v>
       </c>
-      <c r="C27" s="37" t="s">
+      <c r="C35" s="37" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="32" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="B28" s="35">
+      <c r="B36" s="35">
         <v>1.3776999999999999</v>
       </c>
-      <c r="C28" s="38">
-        <v>0</v>
-      </c>
-      <c r="D28" s="122"/>
-      <c r="K28" s="97"/>
-      <c r="N28" s="97"/>
-      <c r="Q28" s="97"/>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="32" t="s">
+      <c r="C36" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="B29" s="35">
+      <c r="B37" s="35">
         <v>1.4671000000000001</v>
       </c>
-      <c r="C29" s="38">
-        <v>0</v>
-      </c>
-      <c r="D29" s="122"/>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" s="32" t="s">
+      <c r="C37" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="32" t="s">
         <v>130</v>
       </c>
-      <c r="B30" s="35">
+      <c r="B38" s="35">
         <v>1.6165</v>
       </c>
-      <c r="C30" s="38">
-        <v>0</v>
-      </c>
-      <c r="D30" s="122"/>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="32" t="s">
+      <c r="C38" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="B31" s="35">
+      <c r="B39" s="35">
         <v>1.9965999999999999</v>
       </c>
-      <c r="C31" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" s="32" t="s">
+      <c r="C39" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="B32" s="35">
+      <c r="B40" s="35">
         <v>2.3096999999999999</v>
       </c>
-      <c r="C32" s="118">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="46" t="s">
+      <c r="C40" s="118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="B33" s="189">
+      <c r="B41" s="138">
         <v>3.3696739999999998</v>
       </c>
-      <c r="C33" s="45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="32" t="s">
+      <c r="C41" s="45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="32" t="s">
         <v>134</v>
       </c>
-      <c r="B34" s="35">
+      <c r="B42" s="35">
         <v>4.3080999999999996</v>
       </c>
-      <c r="C34" s="38">
+      <c r="C42" s="38">
         <v>9.7441000000000003E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="32" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="B35" s="35">
+      <c r="B43" s="35">
         <v>3.9016999999999999</v>
       </c>
-      <c r="C35" s="38">
+      <c r="C43" s="38">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:R1"/>
+    <mergeCell ref="H1:H2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="B1:B2"/>
     <mergeCell ref="F1:F2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="G1:G2"/>
   </mergeCells>
-  <conditionalFormatting sqref="K1:K1048576">
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="L1:L1048576">
     <cfRule type="top10" dxfId="16" priority="1" percent="1" rank="25"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8293,51 +8586,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="145" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="153" t="s">
+      <c r="A1" s="148" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="150" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="147" t="s">
+      <c r="C1" s="152" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="140" t="s">
+      <c r="D1" s="145" t="s">
         <v>98</v>
       </c>
-      <c r="E1" s="141" t="s">
+      <c r="E1" s="146" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="151" t="s">
+      <c r="F1" s="155" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="155" t="s">
+      <c r="G1" s="158" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="140" t="s">
+      <c r="H1" s="145" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="141"/>
-      <c r="J1" s="142"/>
-      <c r="K1" s="140" t="s">
+      <c r="I1" s="146"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="145" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="141"/>
-      <c r="M1" s="142"/>
-      <c r="N1" s="140" t="s">
+      <c r="L1" s="146"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="145" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="141"/>
-      <c r="P1" s="142"/>
+      <c r="O1" s="146"/>
+      <c r="P1" s="147"/>
     </row>
     <row r="2" spans="1:21" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="146"/>
-      <c r="B2" s="154"/>
-      <c r="C2" s="148"/>
-      <c r="D2" s="149"/>
-      <c r="E2" s="150"/>
-      <c r="F2" s="152"/>
-      <c r="G2" s="156"/>
+      <c r="A2" s="149"/>
+      <c r="B2" s="151"/>
+      <c r="C2" s="153"/>
+      <c r="D2" s="157"/>
+      <c r="E2" s="154"/>
+      <c r="F2" s="156"/>
+      <c r="G2" s="159"/>
       <c r="H2" s="111" t="s">
         <v>36</v>
       </c>
@@ -8365,10 +8658,10 @@
       <c r="P2" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="150"/>
-      <c r="S2" s="150"/>
-      <c r="T2" s="150"/>
-      <c r="U2" s="150"/>
+      <c r="R2" s="154"/>
+      <c r="S2" s="154"/>
+      <c r="T2" s="154"/>
+      <c r="U2" s="154"/>
     </row>
     <row r="3" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="30">
@@ -8925,65 +9218,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="145" t="s">
+      <c r="A1" s="148" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="147" t="s">
+      <c r="C1" s="152" t="s">
         <v>69</v>
       </c>
       <c r="D1" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="140" t="s">
+      <c r="E1" s="145" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="141" t="s">
+      <c r="F1" s="146" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="151" t="s">
+      <c r="G1" s="155" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="157" t="s">
+      <c r="H1" s="160" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="141" t="s">
+      <c r="I1" s="146" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="155" t="s">
+      <c r="J1" s="158" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="140" t="s">
+      <c r="K1" s="145" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="141"/>
-      <c r="M1" s="142"/>
-      <c r="N1" s="140" t="s">
+      <c r="L1" s="146"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="145" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="141"/>
-      <c r="P1" s="142"/>
-      <c r="Q1" s="140" t="s">
+      <c r="O1" s="146"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="145" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="141"/>
-      <c r="S1" s="142"/>
-      <c r="T1" s="145" t="s">
+      <c r="R1" s="146"/>
+      <c r="S1" s="147"/>
+      <c r="T1" s="148" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:25" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="146"/>
+      <c r="A2" s="149"/>
       <c r="B2" s="86"/>
-      <c r="C2" s="148"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="150"/>
-      <c r="G2" s="152"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="150"/>
-      <c r="J2" s="156"/>
+      <c r="C2" s="153"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="154"/>
+      <c r="G2" s="156"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="154"/>
+      <c r="J2" s="159"/>
       <c r="K2" s="111" t="s">
         <v>36</v>
       </c>
@@ -9011,11 +9304,11 @@
       <c r="S2" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="T2" s="146"/>
-      <c r="V2" s="150"/>
-      <c r="W2" s="150"/>
-      <c r="X2" s="150"/>
-      <c r="Y2" s="150"/>
+      <c r="T2" s="149"/>
+      <c r="V2" s="154"/>
+      <c r="W2" s="154"/>
+      <c r="X2" s="154"/>
+      <c r="Y2" s="154"/>
     </row>
     <row r="3" spans="1:25" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="30">
@@ -10283,11 +10576,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="Q1:S1"/>
     <mergeCell ref="T1:T2"/>
     <mergeCell ref="V2:W2"/>
     <mergeCell ref="X2:Y2"/>
@@ -10297,6 +10585,11 @@
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="K1:M1"/>
     <mergeCell ref="N1:P1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="Q1:S1"/>
   </mergeCells>
   <conditionalFormatting sqref="M1:M1048576">
     <cfRule type="top10" dxfId="14" priority="1" percent="1" rank="25"/>
@@ -10336,65 +10629,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="145" t="s">
+      <c r="A1" s="148" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="160" t="s">
+      <c r="C1" s="163" t="s">
         <v>69</v>
       </c>
       <c r="D1" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="140" t="s">
+      <c r="E1" s="145" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="141" t="s">
+      <c r="F1" s="146" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="151" t="s">
+      <c r="G1" s="155" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="159" t="s">
+      <c r="H1" s="162" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="141" t="s">
+      <c r="I1" s="146" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="155" t="s">
+      <c r="J1" s="158" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="140" t="s">
+      <c r="K1" s="145" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="141"/>
-      <c r="M1" s="142"/>
-      <c r="N1" s="140" t="s">
+      <c r="L1" s="146"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="145" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="141"/>
-      <c r="P1" s="142"/>
-      <c r="Q1" s="140" t="s">
+      <c r="O1" s="146"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="145" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="141"/>
-      <c r="S1" s="142"/>
-      <c r="T1" s="145" t="s">
+      <c r="R1" s="146"/>
+      <c r="S1" s="147"/>
+      <c r="T1" s="148" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:25" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="146"/>
+      <c r="A2" s="149"/>
       <c r="B2" s="115"/>
-      <c r="C2" s="161"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="150"/>
-      <c r="G2" s="152"/>
-      <c r="H2" s="146"/>
-      <c r="I2" s="150"/>
-      <c r="J2" s="156"/>
+      <c r="C2" s="164"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="154"/>
+      <c r="G2" s="156"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="154"/>
+      <c r="J2" s="159"/>
       <c r="K2" s="111" t="s">
         <v>36</v>
       </c>
@@ -10422,11 +10715,11 @@
       <c r="S2" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="T2" s="146"/>
-      <c r="V2" s="150"/>
-      <c r="W2" s="150"/>
-      <c r="X2" s="150"/>
-      <c r="Y2" s="150"/>
+      <c r="T2" s="149"/>
+      <c r="V2" s="154"/>
+      <c r="W2" s="154"/>
+      <c r="X2" s="154"/>
+      <c r="Y2" s="154"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="32">
@@ -11349,12 +11642,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
     <mergeCell ref="V2:W2"/>
     <mergeCell ref="X2:Y2"/>
     <mergeCell ref="I1:I2"/>
@@ -11363,6 +11650,12 @@
     <mergeCell ref="N1:P1"/>
     <mergeCell ref="Q1:S1"/>
     <mergeCell ref="T1:T2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="M4:M17">
@@ -11410,65 +11703,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="145" t="s">
+      <c r="A1" s="148" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="160" t="s">
+      <c r="C1" s="163" t="s">
         <v>69</v>
       </c>
       <c r="D1" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="140" t="s">
+      <c r="E1" s="145" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="141" t="s">
+      <c r="F1" s="146" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="151" t="s">
+      <c r="G1" s="155" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="159" t="s">
+      <c r="H1" s="162" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="141" t="s">
+      <c r="I1" s="146" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="155" t="s">
+      <c r="J1" s="158" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="140" t="s">
+      <c r="K1" s="145" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="141"/>
-      <c r="M1" s="142"/>
-      <c r="N1" s="140" t="s">
+      <c r="L1" s="146"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="145" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="141"/>
-      <c r="P1" s="142"/>
-      <c r="Q1" s="140" t="s">
+      <c r="O1" s="146"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="145" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="141"/>
-      <c r="S1" s="142"/>
-      <c r="T1" s="145" t="s">
+      <c r="R1" s="146"/>
+      <c r="S1" s="147"/>
+      <c r="T1" s="148" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:25" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="146"/>
+      <c r="A2" s="149"/>
       <c r="B2" s="115"/>
-      <c r="C2" s="161"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="150"/>
-      <c r="G2" s="152"/>
-      <c r="H2" s="146"/>
-      <c r="I2" s="150"/>
-      <c r="J2" s="156"/>
+      <c r="C2" s="164"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="154"/>
+      <c r="G2" s="156"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="154"/>
+      <c r="J2" s="159"/>
       <c r="K2" s="111" t="s">
         <v>36</v>
       </c>
@@ -11496,11 +11789,11 @@
       <c r="S2" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="T2" s="146"/>
-      <c r="V2" s="150"/>
-      <c r="W2" s="150"/>
-      <c r="X2" s="150"/>
-      <c r="Y2" s="150"/>
+      <c r="T2" s="149"/>
+      <c r="V2" s="154"/>
+      <c r="W2" s="154"/>
+      <c r="X2" s="154"/>
+      <c r="Y2" s="154"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="32">
@@ -12164,12 +12457,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
     <mergeCell ref="V2:W2"/>
     <mergeCell ref="X2:Y2"/>
     <mergeCell ref="I1:I2"/>
@@ -12178,6 +12465,12 @@
     <mergeCell ref="N1:P1"/>
     <mergeCell ref="Q1:S1"/>
     <mergeCell ref="T1:T2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
   </mergeCells>
   <conditionalFormatting sqref="M4:M12">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="greaterThan">
@@ -12224,65 +12517,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="145" t="s">
+      <c r="A1" s="148" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="160" t="s">
+      <c r="C1" s="163" t="s">
         <v>69</v>
       </c>
       <c r="D1" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="140" t="s">
+      <c r="E1" s="145" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="141" t="s">
+      <c r="F1" s="146" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="151" t="s">
+      <c r="G1" s="155" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="159" t="s">
+      <c r="H1" s="162" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="141" t="s">
+      <c r="I1" s="146" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="155" t="s">
+      <c r="J1" s="158" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="140" t="s">
+      <c r="K1" s="145" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="141"/>
-      <c r="M1" s="142"/>
-      <c r="N1" s="140" t="s">
+      <c r="L1" s="146"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="145" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="141"/>
-      <c r="P1" s="142"/>
-      <c r="Q1" s="140" t="s">
+      <c r="O1" s="146"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="145" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="141"/>
-      <c r="S1" s="142"/>
-      <c r="T1" s="145" t="s">
+      <c r="R1" s="146"/>
+      <c r="S1" s="147"/>
+      <c r="T1" s="148" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:25" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="146"/>
+      <c r="A2" s="149"/>
       <c r="B2" s="115"/>
-      <c r="C2" s="161"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="150"/>
-      <c r="G2" s="152"/>
-      <c r="H2" s="146"/>
-      <c r="I2" s="150"/>
-      <c r="J2" s="156"/>
+      <c r="C2" s="164"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="154"/>
+      <c r="G2" s="156"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="154"/>
+      <c r="J2" s="159"/>
       <c r="K2" s="111" t="s">
         <v>36</v>
       </c>
@@ -12310,11 +12603,11 @@
       <c r="S2" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="T2" s="146"/>
-      <c r="V2" s="150"/>
-      <c r="W2" s="150"/>
-      <c r="X2" s="150"/>
-      <c r="Y2" s="150"/>
+      <c r="T2" s="149"/>
+      <c r="V2" s="154"/>
+      <c r="W2" s="154"/>
+      <c r="X2" s="154"/>
+      <c r="Y2" s="154"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="32">
@@ -12857,6 +13150,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
     <mergeCell ref="V2:W2"/>
     <mergeCell ref="X2:Y2"/>
     <mergeCell ref="I1:I2"/>
@@ -12865,12 +13164,6 @@
     <mergeCell ref="N1:P1"/>
     <mergeCell ref="Q1:S1"/>
     <mergeCell ref="T1:T2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
   </mergeCells>
   <conditionalFormatting sqref="M4:M7 M10:M11">
     <cfRule type="cellIs" dxfId="9" priority="1" operator="greaterThan">
@@ -12917,65 +13210,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="145" t="s">
+      <c r="A1" s="148" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="147" t="s">
+      <c r="C1" s="152" t="s">
         <v>69</v>
       </c>
       <c r="D1" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="140" t="s">
+      <c r="E1" s="145" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="141" t="s">
+      <c r="F1" s="146" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="151" t="s">
+      <c r="G1" s="155" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="157" t="s">
+      <c r="H1" s="160" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="141" t="s">
+      <c r="I1" s="146" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="155" t="s">
+      <c r="J1" s="158" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="140" t="s">
+      <c r="K1" s="145" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="141"/>
-      <c r="M1" s="142"/>
-      <c r="N1" s="140" t="s">
+      <c r="L1" s="146"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="145" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="141"/>
-      <c r="P1" s="142"/>
-      <c r="Q1" s="140" t="s">
+      <c r="O1" s="146"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="145" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="141"/>
-      <c r="S1" s="142"/>
-      <c r="T1" s="153" t="s">
+      <c r="R1" s="146"/>
+      <c r="S1" s="147"/>
+      <c r="T1" s="150" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:25" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="146"/>
+      <c r="A2" s="149"/>
       <c r="B2" s="86"/>
-      <c r="C2" s="148"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="150"/>
-      <c r="G2" s="152"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="150"/>
-      <c r="J2" s="156"/>
+      <c r="C2" s="153"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="154"/>
+      <c r="G2" s="156"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="154"/>
+      <c r="J2" s="159"/>
       <c r="K2" s="111" t="s">
         <v>36</v>
       </c>
@@ -13003,11 +13296,11 @@
       <c r="S2" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="T2" s="154"/>
-      <c r="V2" s="150"/>
-      <c r="W2" s="150"/>
-      <c r="X2" s="150"/>
-      <c r="Y2" s="150"/>
+      <c r="T2" s="151"/>
+      <c r="V2" s="154"/>
+      <c r="W2" s="154"/>
+      <c r="X2" s="154"/>
+      <c r="Y2" s="154"/>
     </row>
     <row r="3" spans="1:25" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="30">
@@ -14247,12 +14540,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
     <mergeCell ref="V2:W2"/>
     <mergeCell ref="X2:Y2"/>
     <mergeCell ref="I1:I2"/>
@@ -14261,6 +14548,12 @@
     <mergeCell ref="N1:P1"/>
     <mergeCell ref="Q1:S1"/>
     <mergeCell ref="T1:T2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
   </mergeCells>
   <conditionalFormatting sqref="M4:M17 M19">
     <cfRule type="cellIs" dxfId="7" priority="5" operator="greaterThan">
@@ -14317,66 +14610,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="166" t="s">
+      <c r="A1" s="169" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="145" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="167" t="s">
+      <c r="B1" s="148" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="170" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="147" t="s">
+      <c r="D1" s="152" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="140" t="s">
+      <c r="E1" s="145" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="141" t="s">
+      <c r="F1" s="146" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="159" t="s">
+      <c r="G1" s="162" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="159" t="s">
+      <c r="H1" s="162" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="141" t="s">
+      <c r="I1" s="146" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="155" t="s">
+      <c r="J1" s="158" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="140" t="s">
+      <c r="K1" s="145" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="141"/>
-      <c r="M1" s="142"/>
-      <c r="N1" s="140" t="s">
+      <c r="L1" s="146"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="145" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="141"/>
-      <c r="P1" s="142"/>
-      <c r="Q1" s="140" t="s">
+      <c r="O1" s="146"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="145" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="141"/>
-      <c r="S1" s="142"/>
-      <c r="T1" s="166" t="s">
+      <c r="R1" s="146"/>
+      <c r="S1" s="147"/>
+      <c r="T1" s="169" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:25" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="150"/>
-      <c r="B2" s="146"/>
-      <c r="C2" s="161"/>
-      <c r="D2" s="148"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="150"/>
-      <c r="G2" s="146"/>
-      <c r="H2" s="146"/>
-      <c r="I2" s="150"/>
-      <c r="J2" s="156"/>
+      <c r="A2" s="154"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="164"/>
+      <c r="D2" s="153"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="154"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="154"/>
+      <c r="J2" s="159"/>
       <c r="K2" s="39" t="s">
         <v>36</v>
       </c>
@@ -14404,11 +14697,11 @@
       <c r="S2" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="T2" s="150"/>
-      <c r="V2" s="150"/>
-      <c r="W2" s="150"/>
-      <c r="X2" s="150"/>
-      <c r="Y2" s="150"/>
+      <c r="T2" s="154"/>
+      <c r="V2" s="154"/>
+      <c r="W2" s="154"/>
+      <c r="X2" s="154"/>
+      <c r="Y2" s="154"/>
     </row>
     <row r="3" spans="1:25" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="46">
@@ -14478,16 +14771,16 @@
       <c r="D4" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="162">
+      <c r="E4" s="166">
         <v>32.700000000000003</v>
       </c>
-      <c r="F4" s="163">
+      <c r="F4" s="167">
         <v>90.1</v>
       </c>
-      <c r="G4" s="165">
+      <c r="G4" s="168">
         <v>38.5</v>
       </c>
-      <c r="H4" s="165"/>
+      <c r="H4" s="168"/>
       <c r="I4" s="66">
         <v>18.3</v>
       </c>
@@ -14530,12 +14823,12 @@
       <c r="D5" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="162"/>
-      <c r="F5" s="163"/>
-      <c r="G5" s="164">
+      <c r="E5" s="166"/>
+      <c r="F5" s="167"/>
+      <c r="G5" s="165">
         <v>41.2</v>
       </c>
-      <c r="H5" s="164"/>
+      <c r="H5" s="165"/>
       <c r="I5" s="58">
         <v>15.1</v>
       </c>
@@ -14580,12 +14873,12 @@
       <c r="D6" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="162"/>
-      <c r="F6" s="163"/>
-      <c r="G6" s="164">
+      <c r="E6" s="166"/>
+      <c r="F6" s="167"/>
+      <c r="G6" s="165">
         <v>24.3</v>
       </c>
-      <c r="H6" s="164"/>
+      <c r="H6" s="165"/>
       <c r="I6" s="58">
         <v>30.6</v>
       </c>
@@ -14627,12 +14920,12 @@
       <c r="D7" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="162"/>
-      <c r="F7" s="163"/>
-      <c r="G7" s="164">
+      <c r="E7" s="166"/>
+      <c r="F7" s="167"/>
+      <c r="G7" s="165">
         <v>42.6</v>
       </c>
-      <c r="H7" s="164"/>
+      <c r="H7" s="165"/>
       <c r="I7" s="58">
         <v>13.3</v>
       </c>
@@ -14676,12 +14969,12 @@
       <c r="D8" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="162"/>
-      <c r="F8" s="163"/>
-      <c r="G8" s="164">
+      <c r="E8" s="166"/>
+      <c r="F8" s="167"/>
+      <c r="G8" s="165">
         <v>31.9</v>
       </c>
-      <c r="H8" s="164"/>
+      <c r="H8" s="165"/>
       <c r="I8" s="58">
         <v>23.7</v>
       </c>
@@ -14723,8 +15016,8 @@
       <c r="D9" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="162"/>
-      <c r="F9" s="163"/>
+      <c r="E9" s="166"/>
+      <c r="F9" s="167"/>
       <c r="G9" s="66">
         <v>2.7</v>
       </c>
@@ -14773,8 +15066,8 @@
       <c r="D10" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="162"/>
-      <c r="F10" s="163"/>
+      <c r="E10" s="166"/>
+      <c r="F10" s="167"/>
       <c r="G10" s="58">
         <v>4.2</v>
       </c>
@@ -14823,8 +15116,8 @@
       <c r="D11" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="E11" s="162"/>
-      <c r="F11" s="163"/>
+      <c r="E11" s="166"/>
+      <c r="F11" s="167"/>
       <c r="G11" s="58">
         <v>1.3</v>
       </c>
@@ -14942,16 +15235,16 @@
       <c r="D14" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="162">
+      <c r="E14" s="166">
         <v>66.599999999999994</v>
       </c>
-      <c r="F14" s="163">
+      <c r="F14" s="167">
         <v>181.3</v>
       </c>
-      <c r="G14" s="164">
+      <c r="G14" s="165">
         <v>107.3</v>
       </c>
-      <c r="H14" s="164"/>
+      <c r="H14" s="165"/>
       <c r="I14" s="58">
         <v>0</v>
       </c>
@@ -14993,12 +15286,12 @@
       <c r="D15" s="81" t="s">
         <v>44</v>
       </c>
-      <c r="E15" s="162"/>
-      <c r="F15" s="163"/>
-      <c r="G15" s="165">
+      <c r="E15" s="166"/>
+      <c r="F15" s="167"/>
+      <c r="G15" s="168">
         <v>68.7</v>
       </c>
-      <c r="H15" s="165"/>
+      <c r="H15" s="168"/>
       <c r="I15" s="66">
         <v>51.9</v>
       </c>
@@ -15041,12 +15334,12 @@
       <c r="D16" s="81" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="162"/>
-      <c r="F16" s="163"/>
-      <c r="G16" s="165">
+      <c r="E16" s="166"/>
+      <c r="F16" s="167"/>
+      <c r="G16" s="168">
         <v>105</v>
       </c>
-      <c r="H16" s="165"/>
+      <c r="H16" s="168"/>
       <c r="I16" s="66">
         <v>0</v>
       </c>
@@ -15089,12 +15382,12 @@
       <c r="D17" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="162"/>
-      <c r="F17" s="163"/>
-      <c r="G17" s="164">
+      <c r="E17" s="166"/>
+      <c r="F17" s="167"/>
+      <c r="G17" s="165">
         <v>65.599999999999994</v>
       </c>
-      <c r="H17" s="164"/>
+      <c r="H17" s="165"/>
       <c r="I17" s="58">
         <v>53.5</v>
       </c>
@@ -15137,8 +15430,8 @@
       <c r="D18" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="E18" s="162"/>
-      <c r="F18" s="163"/>
+      <c r="E18" s="166"/>
+      <c r="F18" s="167"/>
       <c r="G18" s="58">
         <v>42.6</v>
       </c>
@@ -15187,8 +15480,8 @@
       <c r="D19" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="162"/>
-      <c r="F19" s="163"/>
+      <c r="E19" s="166"/>
+      <c r="F19" s="167"/>
       <c r="G19" s="58">
         <v>47.7</v>
       </c>
@@ -15237,8 +15530,8 @@
       <c r="D20" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="162"/>
-      <c r="F20" s="163"/>
+      <c r="E20" s="166"/>
+      <c r="F20" s="167"/>
       <c r="G20" s="58">
         <v>48.7</v>
       </c>
@@ -15394,18 +15687,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="E4:E11"/>
-    <mergeCell ref="F4:F11"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="T1:T2"/>
-    <mergeCell ref="V2:W2"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="E14:E20"/>
+    <mergeCell ref="F14:F20"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G14:H14"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -15417,12 +15704,18 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="E14:E20"/>
-    <mergeCell ref="F14:F20"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="T1:T2"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="E4:E11"/>
+    <mergeCell ref="F4:F11"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="G5:H5"/>
   </mergeCells>
   <conditionalFormatting sqref="M14:M20">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">

--- a/AsymReca_ThkCalc_new.xlsx
+++ b/AsymReca_ThkCalc_new.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2024-ILLUSTRIOUS\My Drive (61050734@kmitl.ac.th)\AsymReca_SbSe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6001A2C2-D615-46B1-BBDA-700EE9B9082D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B1F466-F4E1-4292-B996-181F5C211E0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28200" yWindow="5265" windowWidth="28320" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28200" yWindow="5265" windowWidth="28320" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="532_back" sheetId="15" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="172">
   <si>
     <t>Wavelength (nm)</t>
   </si>
@@ -2133,6 +2133,24 @@
   </si>
   <si>
     <t>N3 SbSe/TiO M3</t>
+  </si>
+  <si>
+    <t>GST_amo</t>
+  </si>
+  <si>
+    <t>GST_cry</t>
+  </si>
+  <si>
+    <t>GST</t>
+  </si>
+  <si>
+    <t>PCM (nm)</t>
+  </si>
+  <si>
+    <t>Vo2_metallic</t>
+  </si>
+  <si>
+    <t>Vo2_insulator</t>
   </si>
 </sst>
 </file>
@@ -2507,7 +2525,7 @@
     <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="188">
+  <cellXfs count="209">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2927,57 +2945,60 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2999,15 +3020,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -3017,6 +3038,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -3026,11 +3053,29 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3044,28 +3089,64 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3074,7 +3155,27 @@
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="20">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3554,59 +3655,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="149" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="150" t="s">
+      <c r="B1" s="157" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="152" t="s">
+      <c r="C1" s="151" t="s">
         <v>121</v>
       </c>
       <c r="D1" s="44" t="s">
         <v>98</v>
       </c>
-      <c r="E1" s="146" t="s">
+      <c r="E1" s="145" t="s">
         <v>29</v>
       </c>
       <c r="F1" s="155" t="s">
         <v>115</v>
       </c>
-      <c r="G1" s="141" t="s">
+      <c r="G1" s="147" t="s">
         <v>116</v>
       </c>
-      <c r="H1" s="143" t="s">
+      <c r="H1" s="142" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="145" t="s">
+      <c r="I1" s="144" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="146"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="145" t="s">
+      <c r="J1" s="145"/>
+      <c r="K1" s="146"/>
+      <c r="L1" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="146"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="145" t="s">
+      <c r="M1" s="145"/>
+      <c r="N1" s="146"/>
+      <c r="O1" s="144" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="146"/>
-      <c r="Q1" s="147"/>
+      <c r="P1" s="145"/>
+      <c r="Q1" s="146"/>
       <c r="S1" s="128"/>
       <c r="T1" s="128"/>
       <c r="U1" s="128"/>
       <c r="V1" s="128"/>
     </row>
     <row r="2" spans="1:22" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="149"/>
-      <c r="B2" s="151"/>
-      <c r="C2" s="153"/>
+      <c r="A2" s="150"/>
+      <c r="B2" s="158"/>
+      <c r="C2" s="152"/>
       <c r="D2" s="44"/>
       <c r="E2" s="154"/>
       <c r="F2" s="156"/>
-      <c r="G2" s="142"/>
-      <c r="H2" s="144"/>
+      <c r="G2" s="148"/>
+      <c r="H2" s="143"/>
       <c r="I2" s="111" t="s">
         <v>36</v>
       </c>
@@ -5261,19 +5362,19 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
   </mergeCells>
   <conditionalFormatting sqref="K35:K1048576 K27:K32 K1:K25">
-    <cfRule type="top10" dxfId="17" priority="9" percent="1" rank="25"/>
+    <cfRule type="top10" dxfId="19" priority="9" percent="1" rank="25"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -5308,66 +5409,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="170" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="148" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="170" t="s">
+      <c r="B1" s="149" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="171" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="152" t="s">
+      <c r="D1" s="151" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="145" t="s">
+      <c r="E1" s="144" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="146" t="s">
+      <c r="F1" s="145" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="162" t="s">
+      <c r="G1" s="163" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="162" t="s">
+      <c r="H1" s="163" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="146" t="s">
+      <c r="I1" s="145" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="158" t="s">
+      <c r="J1" s="159" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="145" t="s">
+      <c r="K1" s="144" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="146"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="145" t="s">
+      <c r="L1" s="145"/>
+      <c r="M1" s="146"/>
+      <c r="N1" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="146"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="145" t="s">
+      <c r="O1" s="145"/>
+      <c r="P1" s="146"/>
+      <c r="Q1" s="144" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="146"/>
-      <c r="S1" s="147"/>
-      <c r="T1" s="174" t="s">
+      <c r="R1" s="145"/>
+      <c r="S1" s="146"/>
+      <c r="T1" s="172" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:25" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="154"/>
-      <c r="B2" s="149"/>
-      <c r="C2" s="164"/>
-      <c r="D2" s="153"/>
-      <c r="E2" s="157"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="165"/>
+      <c r="D2" s="152"/>
+      <c r="E2" s="153"/>
       <c r="F2" s="154"/>
-      <c r="G2" s="149"/>
-      <c r="H2" s="149"/>
+      <c r="G2" s="150"/>
+      <c r="H2" s="150"/>
       <c r="I2" s="154"/>
-      <c r="J2" s="159"/>
+      <c r="J2" s="160"/>
       <c r="K2" s="39" t="s">
         <v>36</v>
       </c>
@@ -5395,7 +5496,7 @@
       <c r="S2" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="T2" s="175"/>
+      <c r="T2" s="173"/>
       <c r="V2" s="154"/>
       <c r="W2" s="154"/>
       <c r="X2" s="154"/>
@@ -5411,10 +5512,10 @@
       <c r="D3" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="171">
-        <v>0</v>
-      </c>
-      <c r="F3" s="173">
+      <c r="E3" s="174">
+        <v>0</v>
+      </c>
+      <c r="F3" s="176">
         <v>0</v>
       </c>
       <c r="G3" s="58">
@@ -5466,8 +5567,8 @@
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="E4" s="172"/>
-      <c r="F4" s="165"/>
+      <c r="E4" s="175"/>
+      <c r="F4" s="168"/>
       <c r="G4" s="58">
         <v>35.6</v>
       </c>
@@ -6265,14 +6366,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="V2:W2"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="T1:T2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="N1:P1"/>
     <mergeCell ref="E9:E19"/>
     <mergeCell ref="F9:F19"/>
     <mergeCell ref="B1:B2"/>
@@ -6287,10 +6380,18 @@
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="T1:T2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="N1:P1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="M9:M19">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
       <formula>0.45</formula>
     </cfRule>
     <cfRule type="cellIs" priority="3" operator="greaterThan">
@@ -6298,7 +6399,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M9:M20">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
       <formula>$M$8</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6320,40 +6421,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A1" s="179" t="s">
+      <c r="A1" s="188" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="179" t="s">
+      <c r="B1" s="188" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="180" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="180" t="s">
+      <c r="C1" s="183" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="183" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="180" t="s">
+      <c r="E1" s="183" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="187" t="s">
+      <c r="F1" s="184" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="187"/>
-      <c r="H1" s="181" t="s">
+      <c r="G1" s="184"/>
+      <c r="H1" s="177" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="181"/>
-      <c r="J1" s="182" t="s">
+      <c r="I1" s="177"/>
+      <c r="J1" s="178" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="182"/>
+      <c r="K1" s="178"/>
     </row>
     <row r="2" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="179"/>
-      <c r="B2" s="179"/>
-      <c r="C2" s="180"/>
-      <c r="D2" s="180"/>
-      <c r="E2" s="180"/>
+      <c r="A2" s="188"/>
+      <c r="B2" s="188"/>
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183"/>
       <c r="F2" s="14" t="s">
         <v>7</v>
       </c>
@@ -6374,16 +6475,16 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="183" t="s">
+      <c r="A3" s="179" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="183">
+      <c r="C3" s="179">
         <v>1550</v>
       </c>
-      <c r="D3" s="183" t="s">
+      <c r="D3" s="179" t="s">
         <v>26</v>
       </c>
       <c r="E3" s="13">
@@ -6409,12 +6510,12 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="184"/>
+      <c r="A4" s="180"/>
       <c r="B4" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="184"/>
-      <c r="D4" s="186"/>
+      <c r="C4" s="180"/>
+      <c r="D4" s="182"/>
       <c r="E4" s="18">
         <v>52</v>
       </c>
@@ -6438,11 +6539,11 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="184"/>
+      <c r="A5" s="180"/>
       <c r="B5" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="184"/>
+      <c r="C5" s="180"/>
       <c r="D5" s="19" t="s">
         <v>14</v>
       </c>
@@ -6470,11 +6571,11 @@
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="185"/>
+      <c r="A6" s="181"/>
       <c r="B6" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="185"/>
+      <c r="C6" s="181"/>
       <c r="D6" s="23" t="s">
         <v>15</v>
       </c>
@@ -6502,16 +6603,16 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="176" t="s">
+      <c r="A7" s="185" t="s">
         <v>23</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="176">
+      <c r="C7" s="185">
         <v>1320</v>
       </c>
-      <c r="D7" s="176" t="s">
+      <c r="D7" s="185" t="s">
         <v>24</v>
       </c>
       <c r="E7" s="3">
@@ -6537,12 +6638,12 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8" s="177"/>
+      <c r="A8" s="186"/>
       <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="177"/>
-      <c r="D8" s="178"/>
+      <c r="C8" s="186"/>
+      <c r="D8" s="187"/>
       <c r="E8" s="1">
         <v>100</v>
       </c>
@@ -6566,11 +6667,11 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" s="177"/>
+      <c r="A9" s="186"/>
       <c r="B9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="177"/>
+      <c r="C9" s="186"/>
       <c r="D9" s="2" t="s">
         <v>15</v>
       </c>
@@ -6598,11 +6699,11 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="177"/>
+      <c r="A10" s="186"/>
       <c r="B10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="177"/>
+      <c r="C10" s="186"/>
       <c r="D10" s="2" t="s">
         <v>25</v>
       </c>
@@ -6630,11 +6731,11 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="178"/>
+      <c r="A11" s="187"/>
       <c r="B11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="178"/>
+      <c r="C11" s="187"/>
       <c r="D11" s="2" t="s">
         <v>21</v>
       </c>
@@ -6663,6 +6764,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="C7:C11"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="C3:C6"/>
@@ -6670,13 +6778,6 @@
     <mergeCell ref="A3:A6"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A7:A11"/>
-    <mergeCell ref="C7:C11"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6695,40 +6796,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="179" t="s">
+      <c r="A1" s="188" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="179" t="s">
+      <c r="B1" s="188" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="180" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="180" t="s">
+      <c r="C1" s="183" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="183" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="180" t="s">
+      <c r="E1" s="183" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="187" t="s">
+      <c r="F1" s="184" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="187"/>
-      <c r="H1" s="181" t="s">
+      <c r="G1" s="184"/>
+      <c r="H1" s="177" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="181"/>
-      <c r="J1" s="182" t="s">
+      <c r="I1" s="177"/>
+      <c r="J1" s="178" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="182"/>
+      <c r="K1" s="178"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="179"/>
-      <c r="B2" s="179"/>
-      <c r="C2" s="180"/>
-      <c r="D2" s="180"/>
-      <c r="E2" s="180"/>
+      <c r="A2" s="188"/>
+      <c r="B2" s="188"/>
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183"/>
       <c r="F2" s="14" t="s">
         <v>7</v>
       </c>
@@ -6749,16 +6850,16 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="176" t="s">
+      <c r="A3" s="185" t="s">
         <v>23</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="176">
+      <c r="C3" s="185">
         <v>1320</v>
       </c>
-      <c r="D3" s="176" t="s">
+      <c r="D3" s="185" t="s">
         <v>24</v>
       </c>
       <c r="E3" s="3">
@@ -6784,12 +6885,12 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="177"/>
+      <c r="A4" s="186"/>
       <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="177"/>
-      <c r="D4" s="178"/>
+      <c r="C4" s="186"/>
+      <c r="D4" s="187"/>
       <c r="E4" s="1">
         <v>100</v>
       </c>
@@ -6813,11 +6914,11 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="177"/>
+      <c r="A5" s="186"/>
       <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="177"/>
+      <c r="C5" s="186"/>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
@@ -6845,11 +6946,11 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="177"/>
+      <c r="A6" s="186"/>
       <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="177"/>
+      <c r="C6" s="186"/>
       <c r="D6" s="2" t="s">
         <v>25</v>
       </c>
@@ -6877,11 +6978,11 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="178"/>
+      <c r="A7" s="187"/>
       <c r="B7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="178"/>
+      <c r="C7" s="187"/>
       <c r="D7" s="2" t="s">
         <v>21</v>
       </c>
@@ -6928,7 +7029,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D6C66A9-86C5-4B44-B720-CA86E494EFA2}">
-  <dimension ref="A1:W43"/>
+  <dimension ref="A1:W31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" style="32" bestFit="1" customWidth="1"/>
@@ -6946,68 +7047,71 @@
     <col min="16" max="17" width="7.28515625" style="92" customWidth="1"/>
     <col min="18" max="18" width="7.28515625" style="41" customWidth="1"/>
     <col min="19" max="19" width="7.28515625" style="35" customWidth="1"/>
-    <col min="20" max="23" width="7.28515625" style="32" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" style="35" customWidth="1"/>
+    <col min="21" max="21" width="10.140625" style="35" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.28515625" style="35" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.28515625" style="32" customWidth="1"/>
     <col min="24" max="16384" width="9.140625" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="149" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="150" t="s">
+      <c r="B1" s="157" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="152" t="s">
+      <c r="C1" s="151" t="s">
         <v>121</v>
       </c>
-      <c r="D1" s="145" t="s">
+      <c r="D1" s="144" t="s">
         <v>98</v>
       </c>
-      <c r="E1" s="146" t="s">
+      <c r="E1" s="145" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="146" t="s">
+      <c r="F1" s="145" t="s">
         <v>16</v>
       </c>
       <c r="G1" s="155" t="s">
         <v>115</v>
       </c>
-      <c r="H1" s="141" t="s">
+      <c r="H1" s="147" t="s">
         <v>116</v>
       </c>
-      <c r="I1" s="143" t="s">
+      <c r="I1" s="142" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="145" t="s">
+      <c r="J1" s="144" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="146"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="145" t="s">
+      <c r="K1" s="145"/>
+      <c r="L1" s="146"/>
+      <c r="M1" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="146"/>
-      <c r="O1" s="147"/>
-      <c r="P1" s="145" t="s">
+      <c r="N1" s="145"/>
+      <c r="O1" s="146"/>
+      <c r="P1" s="144" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="146"/>
-      <c r="R1" s="147"/>
-      <c r="T1" s="128"/>
-      <c r="U1" s="128"/>
-      <c r="V1" s="128"/>
+      <c r="Q1" s="145"/>
+      <c r="R1" s="146"/>
+      <c r="T1" s="72"/>
+      <c r="U1" s="72"/>
+      <c r="V1" s="72"/>
       <c r="W1" s="128"/>
     </row>
     <row r="2" spans="1:23" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="149"/>
-      <c r="B2" s="151"/>
-      <c r="C2" s="153"/>
-      <c r="D2" s="157"/>
+      <c r="A2" s="150"/>
+      <c r="B2" s="158"/>
+      <c r="C2" s="152"/>
+      <c r="D2" s="153"/>
       <c r="E2" s="154"/>
       <c r="F2" s="154"/>
       <c r="G2" s="156"/>
-      <c r="H2" s="142"/>
-      <c r="I2" s="144"/>
+      <c r="H2" s="148"/>
+      <c r="I2" s="143"/>
       <c r="J2" s="111" t="s">
         <v>36</v>
       </c>
@@ -7036,9 +7140,9 @@
         <v>51</v>
       </c>
       <c r="S2" s="129"/>
-      <c r="T2" s="127"/>
-      <c r="U2" s="127"/>
-      <c r="V2" s="127"/>
+      <c r="T2" s="194"/>
+      <c r="U2" s="194"/>
+      <c r="V2" s="194"/>
       <c r="W2" s="127"/>
     </row>
     <row r="3" spans="1:23" s="30" customFormat="1" x14ac:dyDescent="0.25">
@@ -7101,6 +7205,8 @@
       <c r="T3" s="133" t="s">
         <v>112</v>
       </c>
+      <c r="U3" s="69"/>
+      <c r="V3" s="69"/>
     </row>
     <row r="4" spans="1:23" s="30" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="32" t="s">
@@ -7159,6 +7265,8 @@
       <c r="T4" s="130" t="s">
         <v>113</v>
       </c>
+      <c r="U4" s="69"/>
+      <c r="V4" s="69"/>
     </row>
     <row r="5" spans="1:23" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="35"/>
@@ -7214,6 +7322,8 @@
       <c r="T5" s="35" t="s">
         <v>114</v>
       </c>
+      <c r="U5" s="69"/>
+      <c r="V5" s="69"/>
     </row>
     <row r="6" spans="1:23" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="35"/>
@@ -7267,6 +7377,8 @@
         <v>-0.14700000000000002</v>
       </c>
       <c r="T6" s="131"/>
+      <c r="U6" s="69"/>
+      <c r="V6" s="69"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C7" s="81" t="s">
@@ -7319,7 +7431,6 @@
         <f t="shared" si="2"/>
         <v>-0.154</v>
       </c>
-      <c r="T7" s="35"/>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B8" s="71" t="s">
@@ -7375,6 +7486,15 @@
         <f>P8-Q8</f>
         <v>-0.13</v>
       </c>
+      <c r="T8" s="189" t="s">
+        <v>113</v>
+      </c>
+      <c r="U8" s="69" t="s">
+        <v>82</v>
+      </c>
+      <c r="V8" s="190" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B9" s="71" t="s">
@@ -7429,6 +7549,15 @@
       <c r="R9" s="90">
         <f t="shared" si="2"/>
         <v>-0.188</v>
+      </c>
+      <c r="T9" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="U9" s="35">
+        <v>1.3776999999999999</v>
+      </c>
+      <c r="V9" s="191">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
@@ -7439,6 +7568,15 @@
       <c r="L10" s="90"/>
       <c r="O10" s="90"/>
       <c r="R10" s="90"/>
+      <c r="T10" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="U10" s="35">
+        <v>1.4671000000000001</v>
+      </c>
+      <c r="V10" s="191">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C11" s="81" t="s">
@@ -7489,6 +7627,15 @@
         <f>P11-Q11</f>
         <v>-0.153</v>
       </c>
+      <c r="T11" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="U11" s="35">
+        <v>1.6165</v>
+      </c>
+      <c r="V11" s="191">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C12" s="38" t="s">
@@ -7540,12 +7687,30 @@
       <c r="R12" s="90">
         <f>P12-Q12</f>
         <v>-0.154</v>
+      </c>
+      <c r="T12" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="U12" s="35">
+        <v>1.9965999999999999</v>
+      </c>
+      <c r="V12" s="191">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="30"/>
       <c r="G13" s="84"/>
       <c r="H13" s="134"/>
+      <c r="T13" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="U13" s="35">
+        <v>2.3096999999999999</v>
+      </c>
+      <c r="V13" s="192">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B14" s="35" t="s">
@@ -7600,6 +7765,15 @@
       <c r="R14" s="90">
         <f>P14-Q14</f>
         <v>-0.373</v>
+      </c>
+      <c r="T14" s="138" t="s">
+        <v>133</v>
+      </c>
+      <c r="U14" s="138">
+        <v>3.3696739999999998</v>
+      </c>
+      <c r="V14" s="193">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
@@ -7658,6 +7832,15 @@
         <f>P15-Q15</f>
         <v>-0.31999999999999995</v>
       </c>
+      <c r="T15" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="U15" s="35">
+        <v>4.3080999999999996</v>
+      </c>
+      <c r="V15" s="191">
+        <v>9.7441000000000003E-3</v>
+      </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B16" s="35" t="s">
@@ -7714,8 +7897,17 @@
         <f>P16-Q16</f>
         <v>-0.11399999999999999</v>
       </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="T16" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="U16" s="35">
+        <v>3.9016999999999999</v>
+      </c>
+      <c r="V16" s="191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B17" s="35" t="s">
         <v>100</v>
       </c>
@@ -7771,12 +7963,21 @@
         <v>-4.9999999999999975E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="L18" s="90"/>
       <c r="O18" s="90"/>
       <c r="R18" s="90"/>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="T18" s="35" t="s">
+        <v>166</v>
+      </c>
+      <c r="U18" s="35">
+        <v>4.4375999999999998</v>
+      </c>
+      <c r="V18" s="35">
+        <v>0.49270599999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="32">
         <v>750</v>
       </c>
@@ -7832,8 +8033,17 @@
         <f t="shared" ref="R19:R22" si="7">P19-Q19</f>
         <v>-0.41699999999999998</v>
       </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="T19" s="35" t="s">
+        <v>167</v>
+      </c>
+      <c r="U19" s="35">
+        <v>6.0743999999999998</v>
+      </c>
+      <c r="V19" s="35">
+        <v>2.4540289999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B20" s="35" t="s">
         <v>137</v>
       </c>
@@ -7886,7 +8096,7 @@
         <v>-0.77899999999999991</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B21" s="35" t="s">
         <v>137</v>
       </c>
@@ -7940,11 +8150,11 @@
         <v>-0.8819999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B22" s="35" t="s">
         <v>137</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="C22" s="81" t="s">
         <v>118</v>
       </c>
       <c r="D22" s="44">
@@ -7994,7 +8204,7 @@
         <v>-0.90799999999999992</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B23" s="35" t="s">
         <v>137</v>
       </c>
@@ -8048,7 +8258,7 @@
         <v>-0.91500000000000004</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B24" s="35" t="s">
         <v>137</v>
       </c>
@@ -8102,7 +8312,7 @@
         <v>-0.91399999999999992</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B25" s="35" t="s">
         <v>137</v>
       </c>
@@ -8156,12 +8366,12 @@
         <v>-0.91100000000000003</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="L26" s="90"/>
       <c r="O26" s="90"/>
       <c r="R26" s="90"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" s="32">
         <v>1064</v>
       </c>
@@ -8194,7 +8404,7 @@
         <v>0.51200000000000001</v>
       </c>
       <c r="L27" s="90">
-        <f t="shared" ref="L26:L31" si="11">J27-K27</f>
+        <f t="shared" ref="L27:L31" si="11">J27-K27</f>
         <v>0.42300000000000004</v>
       </c>
       <c r="M27" s="92">
@@ -8204,7 +8414,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="O27" s="90">
-        <f t="shared" ref="O26:O31" si="12">M27-N27</f>
+        <f t="shared" ref="O27:O31" si="12">M27-N27</f>
         <v>-1.2999999999999999E-2</v>
       </c>
       <c r="P27" s="92">
@@ -8214,11 +8424,11 @@
         <v>0.47499999999999998</v>
       </c>
       <c r="R27" s="90">
-        <f t="shared" ref="R26:R31" si="13">P27-Q27</f>
+        <f t="shared" ref="R27:R31" si="13">P27-Q27</f>
         <v>-0.41</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" s="35" t="s">
         <v>159</v>
       </c>
@@ -8272,7 +8482,7 @@
         <v>-0.60799999999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" s="35" t="s">
         <v>161</v>
       </c>
@@ -8329,7 +8539,7 @@
         <v>-0.121</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="35" t="s">
         <v>138</v>
       </c>
@@ -8386,7 +8596,7 @@
         <v>-0.45599999999999996</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C31" s="81" t="s">
         <v>165</v>
       </c>
@@ -8440,112 +8650,8 @@
         <v>-0.84</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="140" t="s">
-        <v>113</v>
-      </c>
-      <c r="B35" s="69" t="s">
-        <v>82</v>
-      </c>
-      <c r="C35" s="37" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="32" t="s">
-        <v>128</v>
-      </c>
-      <c r="B36" s="35">
-        <v>1.3776999999999999</v>
-      </c>
-      <c r="C36" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="B37" s="35">
-        <v>1.4671000000000001</v>
-      </c>
-      <c r="C37" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="32" t="s">
-        <v>130</v>
-      </c>
-      <c r="B38" s="35">
-        <v>1.6165</v>
-      </c>
-      <c r="C38" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="32" t="s">
-        <v>131</v>
-      </c>
-      <c r="B39" s="35">
-        <v>1.9965999999999999</v>
-      </c>
-      <c r="C39" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="32" t="s">
-        <v>132</v>
-      </c>
-      <c r="B40" s="35">
-        <v>2.3096999999999999</v>
-      </c>
-      <c r="C40" s="118">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="B41" s="138">
-        <v>3.3696739999999998</v>
-      </c>
-      <c r="C41" s="45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="32" t="s">
-        <v>134</v>
-      </c>
-      <c r="B42" s="35">
-        <v>4.3080999999999996</v>
-      </c>
-      <c r="C42" s="38">
-        <v>9.7441000000000003E-3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="B43" s="35">
-        <v>3.9016999999999999</v>
-      </c>
-      <c r="C43" s="38">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="P1:R1"/>
-    <mergeCell ref="H1:H2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
@@ -8553,10 +8659,15 @@
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="F1:F2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:R1"/>
+    <mergeCell ref="H1:H2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L1:L1048576">
-    <cfRule type="top10" dxfId="16" priority="1" percent="1" rank="25"/>
+    <cfRule type="top10" dxfId="18" priority="1" percent="1" rank="25"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8564,111 +8675,127 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7F0F96A-322F-4AD3-A595-EC2EEF5FB330}">
-  <dimension ref="A1:U28"/>
+  <dimension ref="A1:V36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" style="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" style="35" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" style="38" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" style="44" customWidth="1"/>
-    <col min="5" max="5" width="7.7109375" style="34" customWidth="1"/>
-    <col min="6" max="6" width="8.7109375" style="84" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="43" customWidth="1"/>
-    <col min="8" max="8" width="7.28515625" style="91" customWidth="1"/>
-    <col min="9" max="9" width="7.28515625" style="92" customWidth="1"/>
-    <col min="10" max="10" width="7.28515625" style="41" customWidth="1"/>
-    <col min="11" max="12" width="7.28515625" style="92" customWidth="1"/>
-    <col min="13" max="13" width="7.28515625" style="41" customWidth="1"/>
-    <col min="14" max="15" width="7.28515625" style="92" customWidth="1"/>
-    <col min="16" max="16" width="7.28515625" style="41" customWidth="1"/>
-    <col min="17" max="21" width="7.28515625" style="32" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="32"/>
+    <col min="2" max="2" width="12.5703125" style="191" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" style="208" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="7.7109375" style="195" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" style="196" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="197" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" style="198" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" style="198" customWidth="1"/>
+    <col min="10" max="10" width="7.28515625" style="199" customWidth="1"/>
+    <col min="11" max="12" width="7.28515625" style="198" customWidth="1"/>
+    <col min="13" max="13" width="7.28515625" style="199" customWidth="1"/>
+    <col min="14" max="15" width="7.28515625" style="198" customWidth="1"/>
+    <col min="16" max="16" width="7.28515625" style="199" customWidth="1"/>
+    <col min="17" max="17" width="7.28515625" style="32" customWidth="1"/>
+    <col min="18" max="18" width="6.85546875" style="32" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.7109375" style="32" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" style="35" customWidth="1"/>
+    <col min="21" max="21" width="10.140625" style="35" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.28515625" style="35" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="148" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="150" t="s">
+    <row r="1" spans="1:22" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="149" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="157" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="152" t="s">
-        <v>69</v>
-      </c>
-      <c r="D1" s="145" t="s">
+      <c r="C1" s="203" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1" s="144" t="s">
         <v>98</v>
       </c>
-      <c r="E1" s="146" t="s">
+      <c r="E1" s="145" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="155" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="158" t="s">
+      <c r="F1" s="145" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="155" t="s">
+        <v>169</v>
+      </c>
+      <c r="H1" s="147" t="s">
+        <v>116</v>
+      </c>
+      <c r="I1" s="142" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="145" t="s">
+      <c r="J1" s="144" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="146"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="145" t="s">
+      <c r="K1" s="145"/>
+      <c r="L1" s="146"/>
+      <c r="M1" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="146"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="145" t="s">
+      <c r="N1" s="145"/>
+      <c r="O1" s="146"/>
+      <c r="P1" s="144" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="146"/>
-      <c r="P1" s="147"/>
-    </row>
-    <row r="2" spans="1:21" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="149"/>
-      <c r="B2" s="151"/>
-      <c r="C2" s="153"/>
-      <c r="D2" s="157"/>
+      <c r="Q1" s="145"/>
+      <c r="R1" s="146"/>
+      <c r="S1" s="128"/>
+      <c r="T1" s="69"/>
+      <c r="U1" s="69"/>
+      <c r="V1" s="69"/>
+    </row>
+    <row r="2" spans="1:22" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="150"/>
+      <c r="B2" s="158"/>
+      <c r="C2" s="204"/>
+      <c r="D2" s="153"/>
       <c r="E2" s="154"/>
-      <c r="F2" s="156"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="111" t="s">
+      <c r="F2" s="154"/>
+      <c r="G2" s="156"/>
+      <c r="H2" s="148"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="111" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="110" t="s">
+      <c r="K2" s="110" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="51" t="s">
+      <c r="L2" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="K2" s="110" t="s">
+      <c r="M2" s="110" t="s">
         <v>36</v>
       </c>
-      <c r="L2" s="110" t="s">
+      <c r="N2" s="110" t="s">
         <v>37</v>
       </c>
-      <c r="M2" s="52" t="s">
+      <c r="O2" s="52" t="s">
         <v>50</v>
       </c>
-      <c r="N2" s="110" t="s">
+      <c r="P2" s="110" t="s">
         <v>36</v>
       </c>
-      <c r="O2" s="110" t="s">
+      <c r="Q2" s="110" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="52" t="s">
+      <c r="R2" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="154"/>
-      <c r="S2" s="154"/>
-      <c r="T2" s="154"/>
-      <c r="U2" s="154"/>
-    </row>
-    <row r="3" spans="1:21" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S2" s="128"/>
+      <c r="T2" s="173"/>
+      <c r="U2" s="173"/>
+      <c r="V2" s="141"/>
+    </row>
+    <row r="3" spans="1:22" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="30">
-        <v>1064</v>
+        <v>1550</v>
       </c>
       <c r="B3" s="35"/>
-      <c r="C3" s="45" t="s">
+      <c r="C3" s="205" t="s">
         <v>74</v>
       </c>
       <c r="D3" s="82">
@@ -8677,499 +8804,832 @@
       <c r="E3" s="31">
         <v>0</v>
       </c>
-      <c r="F3" s="84">
+      <c r="F3" s="31">
+        <v>0</v>
+      </c>
+      <c r="G3" s="84">
         <v>235.89</v>
       </c>
-      <c r="G3" s="83">
-        <f>F3</f>
+      <c r="H3" s="134">
+        <f>G3</f>
         <v>235.89</v>
       </c>
-      <c r="H3" s="95">
+      <c r="I3" s="135">
+        <f>H3</f>
+        <v>235.89</v>
+      </c>
+      <c r="J3" s="95">
         <v>0.93600000000000005</v>
       </c>
-      <c r="I3" s="96">
+      <c r="K3" s="96">
         <v>0.47499999999999998</v>
       </c>
-      <c r="J3" s="90">
-        <f t="shared" ref="J3:J7" si="0">H3-I3</f>
+      <c r="L3" s="90">
+        <f>J3-K3</f>
         <v>0.46100000000000008</v>
       </c>
-      <c r="K3" s="96">
-        <v>0</v>
-      </c>
-      <c r="L3" s="96">
-        <v>0</v>
-      </c>
-      <c r="M3" s="90">
-        <f t="shared" ref="M3:M7" si="1">K3-L3</f>
+      <c r="M3" s="96">
         <v>0</v>
       </c>
       <c r="N3" s="96">
+        <v>0</v>
+      </c>
+      <c r="O3" s="90">
+        <f>M3-N3</f>
+        <v>0</v>
+      </c>
+      <c r="P3" s="96">
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="O3" s="96">
+      <c r="Q3" s="96">
         <v>0.52500000000000002</v>
       </c>
-      <c r="P3" s="90">
-        <f t="shared" ref="P3:P7" si="2">N3-O3</f>
+      <c r="R3" s="90">
+        <f>P3-Q3</f>
         <v>-0.46100000000000002</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C4" s="38" t="s">
-        <v>105</v>
-      </c>
-      <c r="D4" s="44">
-        <v>169.22</v>
-      </c>
-      <c r="E4" s="34">
-        <v>0</v>
-      </c>
-      <c r="F4" s="84">
-        <v>117.95</v>
-      </c>
-      <c r="G4" s="43">
-        <f>D4+F4</f>
-        <v>287.17</v>
-      </c>
-      <c r="H4" s="91">
-        <v>0.93799999999999994</v>
-      </c>
-      <c r="I4" s="92">
-        <v>0.81200000000000006</v>
-      </c>
-      <c r="J4" s="90">
-        <f t="shared" si="0"/>
-        <v>0.12599999999999989</v>
-      </c>
-      <c r="K4" s="92">
-        <v>0</v>
-      </c>
-      <c r="L4" s="92">
-        <v>0</v>
-      </c>
-      <c r="M4" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N4" s="92">
-        <v>6.2E-2</v>
-      </c>
-      <c r="O4" s="92">
-        <v>0.188</v>
-      </c>
-      <c r="P4" s="90">
-        <f t="shared" si="2"/>
-        <v>-0.126</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B5" s="71" t="s">
-        <v>106</v>
-      </c>
-      <c r="C5" s="38" t="s">
-        <v>105</v>
-      </c>
-      <c r="D5" s="44">
-        <v>239.9</v>
-      </c>
-      <c r="E5" s="34">
-        <v>0</v>
-      </c>
-      <c r="F5" s="84">
-        <v>47.41</v>
-      </c>
-      <c r="G5" s="43">
-        <f>D5+F5</f>
-        <v>287.31</v>
-      </c>
-      <c r="H5" s="91">
-        <v>0.96699999999999997</v>
-      </c>
-      <c r="I5" s="92">
-        <v>0.88800000000000001</v>
-      </c>
-      <c r="J5" s="90">
-        <f t="shared" si="0"/>
-        <v>7.8999999999999959E-2</v>
-      </c>
-      <c r="K5" s="92">
-        <v>0</v>
-      </c>
-      <c r="L5" s="92">
-        <v>0</v>
-      </c>
-      <c r="M5" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N5" s="92">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="O5" s="92">
-        <v>0.112</v>
-      </c>
-      <c r="P5" s="90">
-        <f t="shared" si="2"/>
-        <v>-7.9000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B6" s="71" t="s">
-        <v>106</v>
-      </c>
-      <c r="C6" s="38" t="s">
-        <v>105</v>
-      </c>
-      <c r="D6" s="126">
-        <v>98.51</v>
-      </c>
-      <c r="E6" s="34">
-        <v>0</v>
-      </c>
-      <c r="F6" s="84">
-        <v>185.42</v>
-      </c>
-      <c r="G6" s="43">
-        <f>D6+F6</f>
-        <v>283.93</v>
-      </c>
-      <c r="H6" s="91">
-        <v>0.96699999999999997</v>
-      </c>
-      <c r="I6" s="92">
-        <v>0.80200000000000005</v>
-      </c>
-      <c r="J6" s="90">
-        <f t="shared" si="0"/>
-        <v>0.16499999999999992</v>
-      </c>
-      <c r="K6" s="92">
-        <v>0</v>
-      </c>
-      <c r="L6" s="92">
-        <v>0</v>
-      </c>
-      <c r="M6" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N6" s="92">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="O6" s="92">
-        <v>0.19700000000000001</v>
-      </c>
-      <c r="P6" s="90">
-        <f t="shared" si="2"/>
-        <v>-0.16400000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C7" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="D7" s="44">
-        <v>222.73</v>
-      </c>
-      <c r="E7" s="34">
-        <v>169.22</v>
-      </c>
-      <c r="F7" s="84">
-        <v>117.95</v>
-      </c>
-      <c r="G7" s="43">
-        <f>SUM(D7:F7)</f>
-        <v>509.9</v>
-      </c>
-      <c r="H7" s="91">
-        <v>0.93799999999999994</v>
-      </c>
-      <c r="I7" s="92">
-        <v>0.81100000000000005</v>
-      </c>
-      <c r="J7" s="90">
-        <f t="shared" si="0"/>
-        <v>0.12699999999999989</v>
-      </c>
-      <c r="K7" s="92">
-        <v>0</v>
-      </c>
-      <c r="L7" s="92">
-        <v>0</v>
-      </c>
-      <c r="M7" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N7" s="92">
-        <v>6.2E-2</v>
-      </c>
-      <c r="O7" s="92">
-        <v>0.188</v>
-      </c>
-      <c r="P7" s="90">
-        <f t="shared" si="2"/>
-        <v>-0.126</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="30"/>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B9" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="C9" s="38" t="s">
-        <v>103</v>
-      </c>
-      <c r="D9" s="44">
-        <v>268.3</v>
-      </c>
-      <c r="E9" s="34">
-        <v>281.89999999999998</v>
-      </c>
-      <c r="F9" s="84">
-        <v>235.89</v>
-      </c>
-      <c r="G9" s="43">
-        <f>SUM(D9:F9)</f>
-        <v>786.09</v>
-      </c>
-      <c r="H9" s="91">
-        <v>0.95</v>
-      </c>
-      <c r="I9" s="92">
-        <v>0.66200000000000003</v>
-      </c>
-      <c r="J9" s="90">
-        <f>H9-I9</f>
-        <v>0.28799999999999992</v>
-      </c>
-      <c r="K9" s="92">
-        <v>0</v>
-      </c>
-      <c r="L9" s="92">
-        <v>1E-3</v>
-      </c>
-      <c r="M9" s="90">
-        <f>K9-L9</f>
-        <v>-1E-3</v>
-      </c>
-      <c r="N9" s="92">
-        <v>0.05</v>
-      </c>
-      <c r="O9" s="92">
-        <v>0.33800000000000002</v>
-      </c>
-      <c r="P9" s="90">
-        <f>N9-O9</f>
-        <v>-0.28800000000000003</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" s="30"/>
-      <c r="B10" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="C10" s="38" t="s">
-        <v>102</v>
-      </c>
-      <c r="D10" s="44">
-        <v>240.07</v>
-      </c>
-      <c r="E10" s="34">
-        <v>281.89999999999998</v>
-      </c>
-      <c r="F10" s="84">
-        <v>235.89</v>
-      </c>
-      <c r="G10" s="43">
-        <f>SUM(D10:F10)</f>
-        <v>757.86</v>
-      </c>
-      <c r="H10" s="91">
-        <v>0.96599999999999997</v>
-      </c>
-      <c r="I10" s="92">
-        <v>0.72899999999999998</v>
-      </c>
-      <c r="J10" s="90">
-        <f>H10-I10</f>
-        <v>0.23699999999999999</v>
-      </c>
-      <c r="K10" s="92">
-        <v>0</v>
-      </c>
-      <c r="L10" s="92">
-        <v>0</v>
-      </c>
-      <c r="M10" s="90">
-        <f>K10-L10</f>
-        <v>0</v>
-      </c>
-      <c r="N10" s="92">
-        <v>3.4000000000000002E-2</v>
-      </c>
-      <c r="O10" s="92">
-        <v>0.27100000000000002</v>
-      </c>
-      <c r="P10" s="90">
-        <f>N10-O10</f>
-        <v>-0.23700000000000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B11" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>101</v>
-      </c>
-      <c r="D11" s="44">
-        <v>194.68</v>
-      </c>
-      <c r="E11" s="34">
-        <v>240.07</v>
-      </c>
-      <c r="F11" s="84">
-        <v>235.89</v>
-      </c>
-      <c r="G11" s="43">
-        <f>SUM(D11:F11)</f>
-        <v>670.64</v>
-      </c>
-      <c r="H11" s="91">
-        <v>0.96599999999999997</v>
-      </c>
-      <c r="I11" s="92">
-        <v>0.89600000000000002</v>
-      </c>
-      <c r="J11" s="90">
-        <f>H11-I11</f>
-        <v>6.9999999999999951E-2</v>
-      </c>
-      <c r="K11" s="92">
-        <v>0</v>
-      </c>
-      <c r="L11" s="92">
-        <v>0</v>
-      </c>
-      <c r="M11" s="90">
-        <f>K11-L11</f>
-        <v>0</v>
-      </c>
-      <c r="N11" s="92">
-        <v>3.4000000000000002E-2</v>
-      </c>
-      <c r="O11" s="92">
-        <v>0.104</v>
-      </c>
-      <c r="P11" s="90">
-        <f>N11-O11</f>
-        <v>-6.9999999999999993E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B12" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="D12" s="44">
-        <v>169.22</v>
-      </c>
-      <c r="E12" s="34">
-        <v>194.68</v>
-      </c>
-      <c r="F12" s="84">
-        <v>235.89</v>
-      </c>
-      <c r="G12" s="43">
-        <f>SUM(D12:F12)</f>
-        <v>599.79</v>
-      </c>
-      <c r="H12" s="91">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="I12" s="92">
-        <v>0.96399999999999997</v>
-      </c>
-      <c r="J12" s="90">
-        <f>H12-I12</f>
-        <v>1.0000000000000009E-3</v>
-      </c>
-      <c r="K12" s="92">
-        <v>0</v>
-      </c>
-      <c r="L12" s="92">
-        <v>0</v>
-      </c>
-      <c r="M12" s="90">
-        <f>K12-L12</f>
-        <v>0</v>
-      </c>
-      <c r="N12" s="92">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="O12" s="92">
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="P12" s="90">
-        <f>N12-O12</f>
-        <v>-9.9999999999999395E-4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B18" s="71"/>
-      <c r="J18" s="97"/>
-      <c r="M18" s="97"/>
-      <c r="P18" s="97"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B19" s="71"/>
-      <c r="J19" s="97"/>
-      <c r="M19" s="97"/>
-      <c r="P19" s="97"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="J20" s="97"/>
-      <c r="M20" s="97"/>
-      <c r="P20" s="97"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="J21" s="97"/>
-      <c r="M21" s="97"/>
-      <c r="P21" s="97"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C23" s="37"/>
-      <c r="D23" s="122"/>
-      <c r="J23" s="97"/>
-      <c r="M23" s="97"/>
-      <c r="P23" s="97"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="30"/>
-      <c r="D24" s="122"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D25" s="122"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="30"/>
-      <c r="C26" s="37"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" s="30"/>
-      <c r="C27" s="118"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="30"/>
+      <c r="S3" s="128"/>
+      <c r="T3" s="133" t="s">
+        <v>112</v>
+      </c>
+      <c r="U3" s="69"/>
+      <c r="V3" s="69"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A4" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B4" s="35"/>
+      <c r="C4" s="206" t="s">
+        <v>168</v>
+      </c>
+      <c r="D4" s="82">
+        <v>0</v>
+      </c>
+      <c r="E4" s="31">
+        <v>0</v>
+      </c>
+      <c r="F4" s="31">
+        <v>0</v>
+      </c>
+      <c r="G4" s="84">
+        <v>190.25</v>
+      </c>
+      <c r="H4" s="134">
+        <f>G4</f>
+        <v>190.25</v>
+      </c>
+      <c r="I4" s="135">
+        <f>H4</f>
+        <v>190.25</v>
+      </c>
+      <c r="J4" s="95">
+        <v>0.91200000000000003</v>
+      </c>
+      <c r="K4" s="96">
+        <v>5.5E-2</v>
+      </c>
+      <c r="L4" s="90">
+        <f>J4-K4</f>
+        <v>0.85699999999999998</v>
+      </c>
+      <c r="M4" s="96">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="N4" s="96">
+        <v>0.309</v>
+      </c>
+      <c r="O4" s="90">
+        <f>M4-N4</f>
+        <v>-0.28699999999999998</v>
+      </c>
+      <c r="P4" s="96">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="Q4" s="96">
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="R4" s="90">
+        <f>P4-Q4</f>
+        <v>-0.57000000000000006</v>
+      </c>
+      <c r="S4" s="128"/>
+      <c r="T4" s="130" t="s">
+        <v>113</v>
+      </c>
+      <c r="U4" s="69"/>
+      <c r="V4" s="69"/>
+    </row>
+    <row r="5" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="30"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="206"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="135"/>
+      <c r="J5" s="95"/>
+      <c r="K5" s="96"/>
+      <c r="L5" s="90"/>
+      <c r="M5" s="96"/>
+      <c r="N5" s="96"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="96"/>
+      <c r="Q5" s="96"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="128"/>
+      <c r="T5" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="U5" s="69"/>
+      <c r="V5" s="69"/>
+    </row>
+    <row r="6" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="30"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="206"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="84"/>
+      <c r="H6" s="134"/>
+      <c r="I6" s="135"/>
+      <c r="J6" s="95"/>
+      <c r="K6" s="96"/>
+      <c r="L6" s="90"/>
+      <c r="M6" s="96"/>
+      <c r="N6" s="96"/>
+      <c r="O6" s="90"/>
+      <c r="P6" s="96"/>
+      <c r="Q6" s="96"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="128"/>
+      <c r="T6" s="131"/>
+      <c r="U6" s="69"/>
+      <c r="V6" s="69"/>
+    </row>
+    <row r="7" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="35"/>
+      <c r="C7" s="206"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="84"/>
+      <c r="H7" s="134"/>
+      <c r="I7" s="136"/>
+      <c r="J7" s="91"/>
+      <c r="K7" s="92"/>
+      <c r="L7" s="90"/>
+      <c r="M7" s="92"/>
+      <c r="N7" s="92"/>
+      <c r="O7" s="90"/>
+      <c r="P7" s="92"/>
+      <c r="Q7" s="92"/>
+      <c r="R7" s="90"/>
+      <c r="S7" s="128"/>
+    </row>
+    <row r="8" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="71"/>
+      <c r="C8" s="206"/>
+      <c r="D8" s="126"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="84"/>
+      <c r="H8" s="134"/>
+      <c r="I8" s="136"/>
+      <c r="J8" s="91"/>
+      <c r="K8" s="92"/>
+      <c r="L8" s="90"/>
+      <c r="M8" s="92"/>
+      <c r="N8" s="92"/>
+      <c r="O8" s="90"/>
+      <c r="P8" s="92"/>
+      <c r="Q8" s="92"/>
+      <c r="R8" s="90"/>
+      <c r="S8" s="128"/>
+      <c r="T8" s="189" t="s">
+        <v>113</v>
+      </c>
+      <c r="U8" s="69" t="s">
+        <v>82</v>
+      </c>
+      <c r="V8" s="190" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="71"/>
+      <c r="C9" s="206"/>
+      <c r="D9" s="126"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="84"/>
+      <c r="H9" s="134"/>
+      <c r="I9" s="136"/>
+      <c r="J9" s="91"/>
+      <c r="K9" s="92"/>
+      <c r="L9" s="90"/>
+      <c r="M9" s="92"/>
+      <c r="N9" s="92"/>
+      <c r="O9" s="90"/>
+      <c r="P9" s="92"/>
+      <c r="Q9" s="92"/>
+      <c r="R9" s="90"/>
+      <c r="S9" s="128"/>
+      <c r="T9" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="V9" s="191"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B10" s="71"/>
+      <c r="C10" s="206"/>
+      <c r="D10" s="126"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="84"/>
+      <c r="H10" s="134"/>
+      <c r="I10" s="136"/>
+      <c r="J10" s="91"/>
+      <c r="K10" s="92"/>
+      <c r="L10" s="90"/>
+      <c r="M10" s="92"/>
+      <c r="N10" s="92"/>
+      <c r="O10" s="90"/>
+      <c r="P10" s="92"/>
+      <c r="Q10" s="92"/>
+      <c r="R10" s="90"/>
+      <c r="S10" s="128"/>
+      <c r="T10" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="V10" s="191"/>
+    </row>
+    <row r="11" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="35"/>
+      <c r="C11" s="206"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="137"/>
+      <c r="I11" s="136"/>
+      <c r="J11" s="91"/>
+      <c r="K11" s="92"/>
+      <c r="L11" s="90"/>
+      <c r="M11" s="92"/>
+      <c r="N11" s="92"/>
+      <c r="O11" s="90"/>
+      <c r="P11" s="92"/>
+      <c r="Q11" s="92"/>
+      <c r="R11" s="90"/>
+      <c r="S11" s="128"/>
+      <c r="T11" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="V11" s="191"/>
+    </row>
+    <row r="12" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="35"/>
+      <c r="C12" s="206"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="134"/>
+      <c r="I12" s="136"/>
+      <c r="J12" s="91"/>
+      <c r="K12" s="92"/>
+      <c r="L12" s="90"/>
+      <c r="M12" s="92"/>
+      <c r="N12" s="92"/>
+      <c r="O12" s="90"/>
+      <c r="P12" s="92"/>
+      <c r="Q12" s="92"/>
+      <c r="R12" s="90"/>
+      <c r="S12" s="128"/>
+      <c r="T12" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="V12" s="191"/>
+    </row>
+    <row r="13" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="30"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="206"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="84"/>
+      <c r="H13" s="134"/>
+      <c r="I13" s="136"/>
+      <c r="J13" s="91"/>
+      <c r="K13" s="92"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="92"/>
+      <c r="N13" s="92"/>
+      <c r="O13" s="41"/>
+      <c r="P13" s="92"/>
+      <c r="Q13" s="92"/>
+      <c r="R13" s="41"/>
+      <c r="S13" s="128"/>
+      <c r="T13" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="V13" s="192"/>
+    </row>
+    <row r="14" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="35"/>
+      <c r="C14" s="206"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="134"/>
+      <c r="I14" s="136"/>
+      <c r="J14" s="91"/>
+      <c r="K14" s="92"/>
+      <c r="L14" s="90"/>
+      <c r="M14" s="92"/>
+      <c r="N14" s="92"/>
+      <c r="O14" s="90"/>
+      <c r="P14" s="92"/>
+      <c r="Q14" s="92"/>
+      <c r="R14" s="90"/>
+      <c r="S14" s="128"/>
+      <c r="T14" s="138" t="s">
+        <v>133</v>
+      </c>
+      <c r="U14" s="138">
+        <v>3.2854000000000001</v>
+      </c>
+      <c r="V14" s="202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="30"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="206"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="134"/>
+      <c r="I15" s="136"/>
+      <c r="J15" s="91"/>
+      <c r="K15" s="92"/>
+      <c r="L15" s="90"/>
+      <c r="M15" s="92"/>
+      <c r="N15" s="92"/>
+      <c r="O15" s="90"/>
+      <c r="P15" s="92"/>
+      <c r="Q15" s="92"/>
+      <c r="R15" s="90"/>
+      <c r="S15" s="128"/>
+      <c r="T15" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="U15" s="35">
+        <v>4.0499000000000001</v>
+      </c>
+      <c r="V15" s="191">
+        <v>2.14E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="35"/>
+      <c r="C16" s="206"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="84"/>
+      <c r="H16" s="134"/>
+      <c r="I16" s="136"/>
+      <c r="J16" s="91"/>
+      <c r="K16" s="92"/>
+      <c r="L16" s="90"/>
+      <c r="M16" s="92"/>
+      <c r="N16" s="92"/>
+      <c r="O16" s="90"/>
+      <c r="P16" s="92"/>
+      <c r="Q16" s="92"/>
+      <c r="R16" s="90"/>
+      <c r="S16" s="128"/>
+      <c r="T16" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="V16" s="191"/>
+    </row>
+    <row r="17" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="35"/>
+      <c r="C17" s="206"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="84"/>
+      <c r="H17" s="134"/>
+      <c r="I17" s="136"/>
+      <c r="J17" s="91"/>
+      <c r="K17" s="92"/>
+      <c r="L17" s="90"/>
+      <c r="M17" s="92"/>
+      <c r="N17" s="92"/>
+      <c r="O17" s="90"/>
+      <c r="P17" s="92"/>
+      <c r="Q17" s="92"/>
+      <c r="R17" s="90"/>
+      <c r="S17" s="128"/>
+    </row>
+    <row r="18" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="35"/>
+      <c r="C18" s="206"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="137"/>
+      <c r="I18" s="136"/>
+      <c r="J18" s="91"/>
+      <c r="K18" s="92"/>
+      <c r="L18" s="90"/>
+      <c r="M18" s="92"/>
+      <c r="N18" s="92"/>
+      <c r="O18" s="90"/>
+      <c r="P18" s="92"/>
+      <c r="Q18" s="92"/>
+      <c r="R18" s="90"/>
+      <c r="S18" s="128"/>
+      <c r="T18" s="35" t="s">
+        <v>166</v>
+      </c>
+      <c r="U18" s="35">
+        <v>4.0735999999999999</v>
+      </c>
+      <c r="V18" s="35">
+        <v>9.1999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="35"/>
+      <c r="C19" s="206"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="137"/>
+      <c r="I19" s="136"/>
+      <c r="J19" s="91"/>
+      <c r="K19" s="92"/>
+      <c r="L19" s="90"/>
+      <c r="M19" s="92"/>
+      <c r="N19" s="92"/>
+      <c r="O19" s="90"/>
+      <c r="P19" s="92"/>
+      <c r="Q19" s="92"/>
+      <c r="R19" s="90"/>
+      <c r="S19" s="128"/>
+      <c r="T19" s="35" t="s">
+        <v>167</v>
+      </c>
+      <c r="U19" s="35">
+        <v>6.4644000000000004</v>
+      </c>
+      <c r="V19" s="35">
+        <v>0.91980200000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="35"/>
+      <c r="C20" s="206"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="137"/>
+      <c r="I20" s="136"/>
+      <c r="J20" s="91"/>
+      <c r="K20" s="92"/>
+      <c r="L20" s="90"/>
+      <c r="M20" s="92"/>
+      <c r="N20" s="92"/>
+      <c r="O20" s="90"/>
+      <c r="P20" s="92"/>
+      <c r="Q20" s="92"/>
+      <c r="R20" s="90"/>
+      <c r="S20" s="128"/>
+    </row>
+    <row r="21" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="35"/>
+      <c r="C21" s="206"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="137"/>
+      <c r="I21" s="136"/>
+      <c r="J21" s="91"/>
+      <c r="K21" s="92"/>
+      <c r="L21" s="90"/>
+      <c r="M21" s="92"/>
+      <c r="N21" s="92"/>
+      <c r="O21" s="90"/>
+      <c r="P21" s="92"/>
+      <c r="Q21" s="92"/>
+      <c r="R21" s="90"/>
+      <c r="S21" s="128"/>
+      <c r="T21" s="35" t="s">
+        <v>171</v>
+      </c>
+      <c r="U21" s="35">
+        <v>2.8593000000000002</v>
+      </c>
+      <c r="V21" s="35">
+        <v>0.28114</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="35"/>
+      <c r="C22" s="206"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="137"/>
+      <c r="I22" s="136"/>
+      <c r="J22" s="91"/>
+      <c r="K22" s="92"/>
+      <c r="L22" s="90"/>
+      <c r="M22" s="92"/>
+      <c r="N22" s="92"/>
+      <c r="O22" s="42"/>
+      <c r="P22" s="92"/>
+      <c r="Q22" s="92"/>
+      <c r="R22" s="42"/>
+      <c r="S22" s="128"/>
+      <c r="T22" s="35" t="s">
+        <v>170</v>
+      </c>
+      <c r="U22" s="35">
+        <v>1.6076999999999999</v>
+      </c>
+      <c r="V22" s="35">
+        <v>2.722073</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="35"/>
+      <c r="C23" s="206"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="137"/>
+      <c r="I23" s="136"/>
+      <c r="J23" s="91"/>
+      <c r="K23" s="92"/>
+      <c r="L23" s="90"/>
+      <c r="M23" s="92"/>
+      <c r="N23" s="92"/>
+      <c r="O23" s="42"/>
+      <c r="P23" s="92"/>
+      <c r="Q23" s="92"/>
+      <c r="R23" s="42"/>
+      <c r="S23" s="128"/>
+    </row>
+    <row r="24" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="35"/>
+      <c r="C24" s="206"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="137"/>
+      <c r="I24" s="136"/>
+      <c r="J24" s="91"/>
+      <c r="K24" s="92"/>
+      <c r="L24" s="90"/>
+      <c r="M24" s="92"/>
+      <c r="N24" s="92"/>
+      <c r="O24" s="90"/>
+      <c r="P24" s="92"/>
+      <c r="Q24" s="92"/>
+      <c r="R24" s="90"/>
+      <c r="S24" s="128"/>
+    </row>
+    <row r="25" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="35"/>
+      <c r="C25" s="206"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="137"/>
+      <c r="I25" s="136"/>
+      <c r="J25" s="91"/>
+      <c r="K25" s="92"/>
+      <c r="L25" s="90"/>
+      <c r="M25" s="92"/>
+      <c r="N25" s="92"/>
+      <c r="O25" s="90"/>
+      <c r="P25" s="92"/>
+      <c r="Q25" s="92"/>
+      <c r="R25" s="90"/>
+      <c r="S25" s="128"/>
+    </row>
+    <row r="26" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="35"/>
+      <c r="C26" s="206"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="137"/>
+      <c r="I26" s="136"/>
+      <c r="J26" s="91"/>
+      <c r="K26" s="92"/>
+      <c r="L26" s="90"/>
+      <c r="M26" s="92"/>
+      <c r="N26" s="92"/>
+      <c r="O26" s="90"/>
+      <c r="P26" s="92"/>
+      <c r="Q26" s="92"/>
+      <c r="R26" s="90"/>
+      <c r="S26" s="128"/>
+    </row>
+    <row r="27" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="35"/>
+      <c r="C27" s="206"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="137"/>
+      <c r="I27" s="136"/>
+      <c r="J27" s="91"/>
+      <c r="K27" s="92"/>
+      <c r="L27" s="90"/>
+      <c r="M27" s="92"/>
+      <c r="N27" s="92"/>
+      <c r="O27" s="90"/>
+      <c r="P27" s="92"/>
+      <c r="Q27" s="92"/>
+      <c r="R27" s="90"/>
+      <c r="S27" s="128"/>
+    </row>
+    <row r="28" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="35"/>
+      <c r="B28" s="35"/>
+      <c r="C28" s="206"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="137"/>
+      <c r="I28" s="136"/>
+      <c r="J28" s="91"/>
+      <c r="K28" s="92"/>
+      <c r="L28" s="90"/>
+      <c r="M28" s="92"/>
+      <c r="N28" s="92"/>
+      <c r="O28" s="90"/>
+      <c r="P28" s="92"/>
+      <c r="Q28" s="92"/>
+      <c r="R28" s="90"/>
+      <c r="S28" s="128"/>
+      <c r="T28" s="189"/>
+      <c r="U28" s="69"/>
+      <c r="V28" s="190"/>
+    </row>
+    <row r="29" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="35"/>
+      <c r="B29" s="35"/>
+      <c r="C29" s="206"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="137"/>
+      <c r="I29" s="136"/>
+      <c r="J29" s="91"/>
+      <c r="K29" s="92"/>
+      <c r="L29" s="90"/>
+      <c r="M29" s="92"/>
+      <c r="N29" s="92"/>
+      <c r="O29" s="90"/>
+      <c r="P29" s="92"/>
+      <c r="Q29" s="92"/>
+      <c r="R29" s="90"/>
+      <c r="S29" s="128"/>
+      <c r="V29" s="191"/>
+    </row>
+    <row r="30" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="35"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="206"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="137"/>
+      <c r="I30" s="136"/>
+      <c r="J30" s="91"/>
+      <c r="K30" s="92"/>
+      <c r="L30" s="90"/>
+      <c r="M30" s="92"/>
+      <c r="N30" s="92"/>
+      <c r="O30" s="90"/>
+      <c r="P30" s="92"/>
+      <c r="Q30" s="92"/>
+      <c r="R30" s="90"/>
+      <c r="S30" s="128"/>
+      <c r="V30" s="191"/>
+    </row>
+    <row r="31" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="35"/>
+      <c r="C31" s="206"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="137"/>
+      <c r="I31" s="136"/>
+      <c r="J31" s="91"/>
+      <c r="K31" s="92"/>
+      <c r="L31" s="90"/>
+      <c r="M31" s="92"/>
+      <c r="N31" s="92"/>
+      <c r="O31" s="90"/>
+      <c r="P31" s="92"/>
+      <c r="Q31" s="92"/>
+      <c r="R31" s="90"/>
+      <c r="S31" s="128"/>
+      <c r="V31" s="191"/>
+    </row>
+    <row r="32" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="128"/>
+      <c r="B32" s="128"/>
+      <c r="C32" s="207"/>
+      <c r="D32" s="128"/>
+      <c r="E32" s="128"/>
+      <c r="F32" s="128"/>
+      <c r="G32" s="128"/>
+      <c r="H32" s="128"/>
+      <c r="I32" s="128"/>
+      <c r="J32" s="128"/>
+      <c r="K32" s="128"/>
+      <c r="L32" s="128"/>
+      <c r="M32" s="128"/>
+      <c r="N32" s="128"/>
+      <c r="O32" s="128"/>
+      <c r="P32" s="128"/>
+      <c r="Q32" s="128"/>
+      <c r="R32" s="128"/>
+      <c r="S32" s="128"/>
+      <c r="V32" s="191"/>
+    </row>
+    <row r="33" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="128"/>
+      <c r="B33" s="128"/>
+      <c r="C33" s="207"/>
+      <c r="D33" s="128"/>
+      <c r="E33" s="128"/>
+      <c r="F33" s="128"/>
+      <c r="G33" s="128"/>
+      <c r="H33" s="128"/>
+      <c r="I33" s="128"/>
+      <c r="J33" s="128"/>
+      <c r="K33" s="128"/>
+      <c r="L33" s="128"/>
+      <c r="M33" s="128"/>
+      <c r="N33" s="128"/>
+      <c r="O33" s="128"/>
+      <c r="P33" s="128"/>
+      <c r="Q33" s="128"/>
+      <c r="R33" s="128"/>
+      <c r="S33" s="128"/>
+      <c r="V33" s="192"/>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="T34" s="200"/>
+      <c r="U34" s="200"/>
+      <c r="V34" s="201"/>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="V35" s="191"/>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="V36" s="191"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="P1:R1"/>
     <mergeCell ref="T2:U2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
@@ -9178,13 +9638,12 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="R2:S2"/>
   </mergeCells>
-  <conditionalFormatting sqref="J15:J1048576 J1:J12">
-    <cfRule type="top10" dxfId="15" priority="1" percent="1" rank="25"/>
+  <conditionalFormatting sqref="J34:J1048576">
+    <cfRule type="top10" dxfId="17" priority="2" percent="1" rank="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L1:L31">
+    <cfRule type="top10" dxfId="0" priority="1" percent="1" rank="25"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9218,65 +9677,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="149" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="152" t="s">
+      <c r="C1" s="151" t="s">
         <v>69</v>
       </c>
       <c r="D1" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="145" t="s">
+      <c r="E1" s="144" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="146" t="s">
+      <c r="F1" s="145" t="s">
         <v>29</v>
       </c>
       <c r="G1" s="155" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="160" t="s">
+      <c r="H1" s="161" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="146" t="s">
+      <c r="I1" s="145" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="158" t="s">
+      <c r="J1" s="159" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="145" t="s">
+      <c r="K1" s="144" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="146"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="145" t="s">
+      <c r="L1" s="145"/>
+      <c r="M1" s="146"/>
+      <c r="N1" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="146"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="145" t="s">
+      <c r="O1" s="145"/>
+      <c r="P1" s="146"/>
+      <c r="Q1" s="144" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="146"/>
-      <c r="S1" s="147"/>
-      <c r="T1" s="148" t="s">
+      <c r="R1" s="145"/>
+      <c r="S1" s="146"/>
+      <c r="T1" s="149" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:25" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="149"/>
+      <c r="A2" s="150"/>
       <c r="B2" s="86"/>
-      <c r="C2" s="153"/>
-      <c r="E2" s="157"/>
+      <c r="C2" s="152"/>
+      <c r="E2" s="153"/>
       <c r="F2" s="154"/>
       <c r="G2" s="156"/>
-      <c r="H2" s="161"/>
+      <c r="H2" s="162"/>
       <c r="I2" s="154"/>
-      <c r="J2" s="159"/>
+      <c r="J2" s="160"/>
       <c r="K2" s="111" t="s">
         <v>36</v>
       </c>
@@ -9304,7 +9763,7 @@
       <c r="S2" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="T2" s="149"/>
+      <c r="T2" s="150"/>
       <c r="V2" s="154"/>
       <c r="W2" s="154"/>
       <c r="X2" s="154"/>
@@ -10576,6 +11035,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="Q1:S1"/>
     <mergeCell ref="T1:T2"/>
     <mergeCell ref="V2:W2"/>
     <mergeCell ref="X2:Y2"/>
@@ -10585,14 +11049,9 @@
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="K1:M1"/>
     <mergeCell ref="N1:P1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="Q1:S1"/>
   </mergeCells>
   <conditionalFormatting sqref="M1:M1048576">
-    <cfRule type="top10" dxfId="14" priority="1" percent="1" rank="25"/>
+    <cfRule type="top10" dxfId="16" priority="1" percent="1" rank="25"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A20" r:id="rId1" xr:uid="{0CA2BC15-2917-4413-A3B6-CA9BB1B2A39C}"/>
@@ -10629,65 +11088,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="149" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="163" t="s">
+      <c r="C1" s="164" t="s">
         <v>69</v>
       </c>
       <c r="D1" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="145" t="s">
+      <c r="E1" s="144" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="146" t="s">
+      <c r="F1" s="145" t="s">
         <v>29</v>
       </c>
       <c r="G1" s="155" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="162" t="s">
+      <c r="H1" s="163" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="146" t="s">
+      <c r="I1" s="145" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="158" t="s">
+      <c r="J1" s="159" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="145" t="s">
+      <c r="K1" s="144" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="146"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="145" t="s">
+      <c r="L1" s="145"/>
+      <c r="M1" s="146"/>
+      <c r="N1" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="146"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="145" t="s">
+      <c r="O1" s="145"/>
+      <c r="P1" s="146"/>
+      <c r="Q1" s="144" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="146"/>
-      <c r="S1" s="147"/>
-      <c r="T1" s="148" t="s">
+      <c r="R1" s="145"/>
+      <c r="S1" s="146"/>
+      <c r="T1" s="149" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:25" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="149"/>
+      <c r="A2" s="150"/>
       <c r="B2" s="115"/>
-      <c r="C2" s="164"/>
-      <c r="E2" s="157"/>
+      <c r="C2" s="165"/>
+      <c r="E2" s="153"/>
       <c r="F2" s="154"/>
       <c r="G2" s="156"/>
-      <c r="H2" s="149"/>
+      <c r="H2" s="150"/>
       <c r="I2" s="154"/>
-      <c r="J2" s="159"/>
+      <c r="J2" s="160"/>
       <c r="K2" s="111" t="s">
         <v>36</v>
       </c>
@@ -10715,7 +11174,7 @@
       <c r="S2" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="T2" s="149"/>
+      <c r="T2" s="150"/>
       <c r="V2" s="154"/>
       <c r="W2" s="154"/>
       <c r="X2" s="154"/>
@@ -11642,6 +12101,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
     <mergeCell ref="V2:W2"/>
     <mergeCell ref="X2:Y2"/>
     <mergeCell ref="I1:I2"/>
@@ -11650,21 +12115,15 @@
     <mergeCell ref="N1:P1"/>
     <mergeCell ref="Q1:S1"/>
     <mergeCell ref="T1:T2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="M4:M17">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="greaterThan">
       <formula>$M$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M23:M25">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="2" operator="greaterThan">
       <formula>0.45</formula>
     </cfRule>
     <cfRule type="cellIs" priority="3" operator="greaterThan">
@@ -11703,65 +12162,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="149" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="163" t="s">
+      <c r="C1" s="164" t="s">
         <v>69</v>
       </c>
       <c r="D1" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="145" t="s">
+      <c r="E1" s="144" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="146" t="s">
+      <c r="F1" s="145" t="s">
         <v>29</v>
       </c>
       <c r="G1" s="155" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="162" t="s">
+      <c r="H1" s="163" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="146" t="s">
+      <c r="I1" s="145" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="158" t="s">
+      <c r="J1" s="159" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="145" t="s">
+      <c r="K1" s="144" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="146"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="145" t="s">
+      <c r="L1" s="145"/>
+      <c r="M1" s="146"/>
+      <c r="N1" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="146"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="145" t="s">
+      <c r="O1" s="145"/>
+      <c r="P1" s="146"/>
+      <c r="Q1" s="144" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="146"/>
-      <c r="S1" s="147"/>
-      <c r="T1" s="148" t="s">
+      <c r="R1" s="145"/>
+      <c r="S1" s="146"/>
+      <c r="T1" s="149" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:25" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="149"/>
+      <c r="A2" s="150"/>
       <c r="B2" s="115"/>
-      <c r="C2" s="164"/>
-      <c r="E2" s="157"/>
+      <c r="C2" s="165"/>
+      <c r="E2" s="153"/>
       <c r="F2" s="154"/>
       <c r="G2" s="156"/>
-      <c r="H2" s="149"/>
+      <c r="H2" s="150"/>
       <c r="I2" s="154"/>
-      <c r="J2" s="159"/>
+      <c r="J2" s="160"/>
       <c r="K2" s="111" t="s">
         <v>36</v>
       </c>
@@ -11789,7 +12248,7 @@
       <c r="S2" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="T2" s="149"/>
+      <c r="T2" s="150"/>
       <c r="V2" s="154"/>
       <c r="W2" s="154"/>
       <c r="X2" s="154"/>
@@ -12457,6 +12916,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
     <mergeCell ref="V2:W2"/>
     <mergeCell ref="X2:Y2"/>
     <mergeCell ref="I1:I2"/>
@@ -12465,20 +12930,14 @@
     <mergeCell ref="N1:P1"/>
     <mergeCell ref="Q1:S1"/>
     <mergeCell ref="T1:T2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
   </mergeCells>
   <conditionalFormatting sqref="M4:M12">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="greaterThan">
       <formula>$M$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M23:M25">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
       <formula>0.45</formula>
     </cfRule>
     <cfRule type="cellIs" priority="3" operator="greaterThan">
@@ -12517,65 +12976,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="149" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="163" t="s">
+      <c r="C1" s="164" t="s">
         <v>69</v>
       </c>
       <c r="D1" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="145" t="s">
+      <c r="E1" s="144" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="146" t="s">
+      <c r="F1" s="145" t="s">
         <v>29</v>
       </c>
       <c r="G1" s="155" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="162" t="s">
+      <c r="H1" s="163" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="146" t="s">
+      <c r="I1" s="145" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="158" t="s">
+      <c r="J1" s="159" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="145" t="s">
+      <c r="K1" s="144" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="146"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="145" t="s">
+      <c r="L1" s="145"/>
+      <c r="M1" s="146"/>
+      <c r="N1" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="146"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="145" t="s">
+      <c r="O1" s="145"/>
+      <c r="P1" s="146"/>
+      <c r="Q1" s="144" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="146"/>
-      <c r="S1" s="147"/>
-      <c r="T1" s="148" t="s">
+      <c r="R1" s="145"/>
+      <c r="S1" s="146"/>
+      <c r="T1" s="149" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:25" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="149"/>
+      <c r="A2" s="150"/>
       <c r="B2" s="115"/>
-      <c r="C2" s="164"/>
-      <c r="E2" s="157"/>
+      <c r="C2" s="165"/>
+      <c r="E2" s="153"/>
       <c r="F2" s="154"/>
       <c r="G2" s="156"/>
-      <c r="H2" s="149"/>
+      <c r="H2" s="150"/>
       <c r="I2" s="154"/>
-      <c r="J2" s="159"/>
+      <c r="J2" s="160"/>
       <c r="K2" s="111" t="s">
         <v>36</v>
       </c>
@@ -12603,7 +13062,7 @@
       <c r="S2" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="T2" s="149"/>
+      <c r="T2" s="150"/>
       <c r="V2" s="154"/>
       <c r="W2" s="154"/>
       <c r="X2" s="154"/>
@@ -13150,12 +13609,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
     <mergeCell ref="V2:W2"/>
     <mergeCell ref="X2:Y2"/>
     <mergeCell ref="I1:I2"/>
@@ -13164,14 +13617,20 @@
     <mergeCell ref="N1:P1"/>
     <mergeCell ref="Q1:S1"/>
     <mergeCell ref="T1:T2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
   </mergeCells>
   <conditionalFormatting sqref="M4:M7 M10:M11">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="greaterThan">
       <formula>$M$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M23:M25">
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="greaterThan">
       <formula>0.45</formula>
     </cfRule>
     <cfRule type="cellIs" priority="3" operator="greaterThan">
@@ -13210,65 +13669,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="149" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="152" t="s">
+      <c r="C1" s="151" t="s">
         <v>69</v>
       </c>
       <c r="D1" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="145" t="s">
+      <c r="E1" s="144" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="146" t="s">
+      <c r="F1" s="145" t="s">
         <v>29</v>
       </c>
       <c r="G1" s="155" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="160" t="s">
+      <c r="H1" s="161" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="146" t="s">
+      <c r="I1" s="145" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="158" t="s">
+      <c r="J1" s="159" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="145" t="s">
+      <c r="K1" s="144" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="146"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="145" t="s">
+      <c r="L1" s="145"/>
+      <c r="M1" s="146"/>
+      <c r="N1" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="146"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="145" t="s">
+      <c r="O1" s="145"/>
+      <c r="P1" s="146"/>
+      <c r="Q1" s="144" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="146"/>
-      <c r="S1" s="147"/>
-      <c r="T1" s="150" t="s">
+      <c r="R1" s="145"/>
+      <c r="S1" s="146"/>
+      <c r="T1" s="157" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:25" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="149"/>
+      <c r="A2" s="150"/>
       <c r="B2" s="86"/>
-      <c r="C2" s="153"/>
-      <c r="E2" s="157"/>
+      <c r="C2" s="152"/>
+      <c r="E2" s="153"/>
       <c r="F2" s="154"/>
       <c r="G2" s="156"/>
-      <c r="H2" s="161"/>
+      <c r="H2" s="162"/>
       <c r="I2" s="154"/>
-      <c r="J2" s="159"/>
+      <c r="J2" s="160"/>
       <c r="K2" s="111" t="s">
         <v>36</v>
       </c>
@@ -13296,7 +13755,7 @@
       <c r="S2" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="T2" s="151"/>
+      <c r="T2" s="158"/>
       <c r="V2" s="154"/>
       <c r="W2" s="154"/>
       <c r="X2" s="154"/>
@@ -14540,6 +14999,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
     <mergeCell ref="V2:W2"/>
     <mergeCell ref="X2:Y2"/>
     <mergeCell ref="I1:I2"/>
@@ -14548,20 +15013,14 @@
     <mergeCell ref="N1:P1"/>
     <mergeCell ref="Q1:S1"/>
     <mergeCell ref="T1:T2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
   </mergeCells>
   <conditionalFormatting sqref="M4:M17 M19">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="5" operator="greaterThan">
       <formula>$M$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M16:M18">
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="6" operator="greaterThan">
       <formula>0.45</formula>
     </cfRule>
     <cfRule type="cellIs" priority="7" operator="greaterThan">
@@ -14569,12 +15028,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M20:M23">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="greaterThan">
       <formula>$M$19</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M24:M25">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="greaterThan">
       <formula>$M$3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14610,66 +15069,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="30" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="170" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="148" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="170" t="s">
+      <c r="B1" s="149" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="171" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="152" t="s">
+      <c r="D1" s="151" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="145" t="s">
+      <c r="E1" s="144" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="146" t="s">
+      <c r="F1" s="145" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="162" t="s">
+      <c r="G1" s="163" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="162" t="s">
+      <c r="H1" s="163" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="146" t="s">
+      <c r="I1" s="145" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="158" t="s">
+      <c r="J1" s="159" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="145" t="s">
+      <c r="K1" s="144" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="146"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="145" t="s">
+      <c r="L1" s="145"/>
+      <c r="M1" s="146"/>
+      <c r="N1" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="146"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="145" t="s">
+      <c r="O1" s="145"/>
+      <c r="P1" s="146"/>
+      <c r="Q1" s="144" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="146"/>
-      <c r="S1" s="147"/>
-      <c r="T1" s="169" t="s">
+      <c r="R1" s="145"/>
+      <c r="S1" s="146"/>
+      <c r="T1" s="170" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:25" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="154"/>
-      <c r="B2" s="149"/>
-      <c r="C2" s="164"/>
-      <c r="D2" s="153"/>
-      <c r="E2" s="157"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="165"/>
+      <c r="D2" s="152"/>
+      <c r="E2" s="153"/>
       <c r="F2" s="154"/>
-      <c r="G2" s="149"/>
-      <c r="H2" s="149"/>
+      <c r="G2" s="150"/>
+      <c r="H2" s="150"/>
       <c r="I2" s="154"/>
-      <c r="J2" s="159"/>
+      <c r="J2" s="160"/>
       <c r="K2" s="39" t="s">
         <v>36</v>
       </c>
@@ -14777,10 +15236,10 @@
       <c r="F4" s="167">
         <v>90.1</v>
       </c>
-      <c r="G4" s="168">
+      <c r="G4" s="169">
         <v>38.5</v>
       </c>
-      <c r="H4" s="168"/>
+      <c r="H4" s="169"/>
       <c r="I4" s="66">
         <v>18.3</v>
       </c>
@@ -14825,10 +15284,10 @@
       </c>
       <c r="E5" s="166"/>
       <c r="F5" s="167"/>
-      <c r="G5" s="165">
+      <c r="G5" s="168">
         <v>41.2</v>
       </c>
-      <c r="H5" s="165"/>
+      <c r="H5" s="168"/>
       <c r="I5" s="58">
         <v>15.1</v>
       </c>
@@ -14875,10 +15334,10 @@
       </c>
       <c r="E6" s="166"/>
       <c r="F6" s="167"/>
-      <c r="G6" s="165">
+      <c r="G6" s="168">
         <v>24.3</v>
       </c>
-      <c r="H6" s="165"/>
+      <c r="H6" s="168"/>
       <c r="I6" s="58">
         <v>30.6</v>
       </c>
@@ -14922,10 +15381,10 @@
       </c>
       <c r="E7" s="166"/>
       <c r="F7" s="167"/>
-      <c r="G7" s="165">
+      <c r="G7" s="168">
         <v>42.6</v>
       </c>
-      <c r="H7" s="165"/>
+      <c r="H7" s="168"/>
       <c r="I7" s="58">
         <v>13.3</v>
       </c>
@@ -14971,10 +15430,10 @@
       </c>
       <c r="E8" s="166"/>
       <c r="F8" s="167"/>
-      <c r="G8" s="165">
+      <c r="G8" s="168">
         <v>31.9</v>
       </c>
-      <c r="H8" s="165"/>
+      <c r="H8" s="168"/>
       <c r="I8" s="58">
         <v>23.7</v>
       </c>
@@ -15241,10 +15700,10 @@
       <c r="F14" s="167">
         <v>181.3</v>
       </c>
-      <c r="G14" s="165">
+      <c r="G14" s="168">
         <v>107.3</v>
       </c>
-      <c r="H14" s="165"/>
+      <c r="H14" s="168"/>
       <c r="I14" s="58">
         <v>0</v>
       </c>
@@ -15288,10 +15747,10 @@
       </c>
       <c r="E15" s="166"/>
       <c r="F15" s="167"/>
-      <c r="G15" s="168">
+      <c r="G15" s="169">
         <v>68.7</v>
       </c>
-      <c r="H15" s="168"/>
+      <c r="H15" s="169"/>
       <c r="I15" s="66">
         <v>51.9</v>
       </c>
@@ -15336,10 +15795,10 @@
       </c>
       <c r="E16" s="166"/>
       <c r="F16" s="167"/>
-      <c r="G16" s="168">
+      <c r="G16" s="169">
         <v>105</v>
       </c>
-      <c r="H16" s="168"/>
+      <c r="H16" s="169"/>
       <c r="I16" s="66">
         <v>0</v>
       </c>
@@ -15384,10 +15843,10 @@
       </c>
       <c r="E17" s="166"/>
       <c r="F17" s="167"/>
-      <c r="G17" s="165">
+      <c r="G17" s="168">
         <v>65.599999999999994</v>
       </c>
-      <c r="H17" s="165"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="58">
         <v>53.5</v>
       </c>
@@ -15687,12 +16146,18 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="E14:E20"/>
-    <mergeCell ref="F14:F20"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="E4:E11"/>
+    <mergeCell ref="F4:F11"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="T1:T2"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="N1:P1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -15704,26 +16169,20 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="T1:T2"/>
-    <mergeCell ref="V2:W2"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="E4:E11"/>
-    <mergeCell ref="F4:F11"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="E14:E20"/>
+    <mergeCell ref="F14:F20"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G14:H14"/>
   </mergeCells>
   <conditionalFormatting sqref="M14:M20">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="greaterThan">
       <formula>$M$13</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M29:M33">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
       <formula>0.45</formula>
     </cfRule>
     <cfRule type="cellIs" priority="3" operator="greaterThan">
